--- a/slidedeck/data/model_slide_data.xlsx
+++ b/slidedeck/data/model_slide_data.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Selected model: logit_elasticnet_binned_ohe_balanced | Baseline: random_classifier</t>
+          <t>Selected model: logit_binned_ohe_balanced_calibrated | Baseline: random_classifier</t>
         </is>
       </c>
     </row>
@@ -86652,32 +86652,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>probit_binned_ohe</t>
+          <t>logit_binned_ohe_balanced</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.881098652646202</v>
+        <v>0.8811365072867504</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004329473006519601</v>
+        <v>0.004376531559578211</v>
       </c>
       <c r="D5" t="n">
-        <v>0.699451296010961</v>
+        <v>0.6979843583264473</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005430496063525884</v>
+        <v>0.005228907087311024</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8408418870339045</v>
+        <v>0.7937369346877954</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002956942389737198</v>
+        <v>0.007635615319973337</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5887628798353282</v>
+        <v>0.643169280418737</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009847891224148293</v>
+        <v>0.01041661405314055</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -86686,32 +86686,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>logit_binned_ohe</t>
+          <t>logit_binned_ohe_balanced_calibrated</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8810525664936373</v>
+        <v>0.881130493247186</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004399871941074101</v>
+        <v>0.004370391028659821</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7000061433590246</v>
+        <v>0.6980576057044253</v>
       </c>
       <c r="E6" t="n">
-        <v>0.005493287863198479</v>
+        <v>0.005206617861945132</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8419347122034452</v>
+        <v>0.8403330948442059</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003374486507193572</v>
+        <v>0.002963045688369091</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5959828291514137</v>
+        <v>0.5876274656093299</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01093835291011654</v>
+        <v>0.01020369228274071</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -86720,32 +86720,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>logit_elasticnet_binned_ohe</t>
+          <t>logit_binned_ohe</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8810395947267043</v>
+        <v>0.8810525664936373</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004397931763937513</v>
+        <v>0.004399871941074101</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7001044823040902</v>
+        <v>0.7000061433590246</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005480282425292697</v>
+        <v>0.005493287863198479</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8418781848660852</v>
+        <v>0.8419347122034452</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003073224702100414</v>
+        <v>0.003374486507193572</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5943442370054564</v>
+        <v>0.5959828291514137</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009979210756378148</v>
+        <v>0.01093835291011654</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -86754,32 +86754,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>logit_elastic_binned_woe_balanced</t>
+          <t>logit_elasticnet_binned_ohe</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8772949445020284</v>
+        <v>0.8810395947267043</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003761449015753651</v>
+        <v>0.004397931763937513</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6915303944720554</v>
+        <v>0.7001044823040902</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003401032940688927</v>
+        <v>0.005480282425292697</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7897235878172972</v>
+        <v>0.8418781848660852</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005722608230804933</v>
+        <v>0.003073224702100414</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6360934863488088</v>
+        <v>0.5943442370054564</v>
       </c>
       <c r="I8" t="n">
-        <v>0.007341581998092306</v>
+        <v>0.009979210756378148</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -86788,32 +86788,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>probit_binned_woe</t>
+          <t>logit_elastic_binned_woe_balanced</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8772493344519861</v>
+        <v>0.8772949445020284</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003758392081015121</v>
+        <v>0.003761449015753651</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6925102310307117</v>
+        <v>0.6915303944720554</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003675010487162835</v>
+        <v>0.003401032940688927</v>
       </c>
       <c r="F9" t="n">
-        <v>0.837129927580784</v>
+        <v>0.7897235878172972</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00250610368814775</v>
+        <v>0.005722608230804933</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5637986152698213</v>
+        <v>0.6360934863488088</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009739962185223975</v>
+        <v>0.007341581998092306</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -86992,32 +86992,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>classic_probit_standard_scaler</t>
+          <t>random_classifier</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8673245004354948</v>
+        <v>0.5018559714056471</v>
       </c>
       <c r="C15" t="n">
-        <v>0.005595635871942865</v>
+        <v>0.001720555585391747</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6723796613221376</v>
+        <v>0.2279191500425641</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01105642907323687</v>
+        <v>0.0006133047160225449</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8273132819627576</v>
+        <v>0.6535903477494552</v>
       </c>
       <c r="G15" t="n">
-        <v>0.002905985714439273</v>
+        <v>0.00121384248121297</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5354782467675043</v>
+        <v>0.2269038960423601</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01099545915970917</v>
+        <v>0.002692826940019715</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -87026,32 +87026,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>random_classifier</t>
+          <t>always_true_classifier</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5018559714056471</v>
+        <v>0.5</v>
       </c>
       <c r="C16" t="n">
-        <v>0.001720555585391747</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2279191500425641</v>
+        <v>0.2272530286210917</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0006133047160225449</v>
+        <v>3.884716467977554e-05</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6535903477494552</v>
+        <v>0.2272530286210917</v>
       </c>
       <c r="G16" t="n">
-        <v>0.00121384248121297</v>
+        <v>3.884716467977554e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2269038960423601</v>
+        <v>0.3703442118613253</v>
       </c>
       <c r="I16" t="n">
-        <v>0.002692826940019715</v>
+        <v>5.158293634861289e-05</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -87126,32 +87126,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>logit_elasticnet_binned_ohe_balanced</t>
+          <t>logit_binned_ohe_balanced_calibrated</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8811585985239313</v>
+        <v>0.881130493247186</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004389213114772924</v>
+        <v>0.004370391028659821</v>
       </c>
       <c r="D2" t="n">
-        <v>0.697863011313659</v>
+        <v>0.6980576057044253</v>
       </c>
       <c r="E2" t="n">
-        <v>0.005226812006440109</v>
+        <v>0.005206617861945132</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7936804073504355</v>
+        <v>0.8403330948442059</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007895207356770791</v>
+        <v>0.002963045688369091</v>
       </c>
       <c r="H2" t="n">
-        <v>0.643112712468934</v>
+        <v>0.5876274656093299</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01065785074699211</v>
+        <v>0.01020369228274071</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -87326,7 +87326,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>logit_elasticnet_binned_ohe_balanced</t>
+          <t>logit_binned_ohe_balanced_calibrated</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -87335,22 +87335,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8771380317718289</v>
+        <v>0.8771122911143998</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6933499882637983</v>
+        <v>0.6933517849967762</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7898971247691902</v>
+        <v>0.8415105952694979</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6373226075738029</v>
+        <v>0.5938943336712853</v>
       </c>
       <c r="G2" t="n">
-        <v>0.524416135881104</v>
+        <v>0.7110871324521176</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8121856866537718</v>
+        <v>0.5098646034816248</v>
       </c>
       <c r="I2" t="n">
         <v>0.5</v>
@@ -87439,17 +87439,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Total Days Identified Through Qualified</t>
+          <t>Supplies Group</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.96208993651416</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-19.96208993651416</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -87458,17 +87458,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sales Stage Change Count</t>
+          <t>Supplies Subgroup</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.397008899365852</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>4.397008899365852</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -87477,17 +87477,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Total Days Identified Through Closing</t>
+          <t>Region</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.64093361361122</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-3.484671207222331</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -87496,17 +87496,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ratio Days Identified To Total Days</t>
+          <t>Route To Market</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.860939495269587</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>-2.860939495269587</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -87515,17 +87515,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ratio Days Validated To Total Days</t>
+          <t>Elapsed Days In Sales Stage</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.418681262343813</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>-2.418681262343813</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -87534,14 +87534,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Revenue From Client Past Two Years (USD)</t>
+          <t>Sales Stage Change Count</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.269152646266659</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>2.269152646266659</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -87553,17 +87553,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Supplies Subgroup</t>
+          <t>Total Days Identified Through Closing</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.581655154384426</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>1.325727326875223</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -87572,17 +87572,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Elapsed Days In Sales Stage</t>
+          <t>Total Days Identified Through Qualified</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.48180286753154</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.8088998831989709</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -87591,17 +87591,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Route To Market</t>
+          <t>Client Size By Revenue (USD)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.052484812839753</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1.052484812839753</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -87610,14 +87610,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ratio Days Qualified To Total Days</t>
+          <t>Client Size By Employee Count</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.880489600858903</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.880489600858903</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -87688,7 +87688,7 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01908913925394608</v>
+        <v>0.006657620624347824</v>
       </c>
       <c r="E2" t="n">
         <v>0.006593406593406593</v>
@@ -87708,19 +87708,19 @@
         <v>2275</v>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05086841906436734</v>
+        <v>0.01749794825832251</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01406593406593407</v>
+        <v>0.01450549450549451</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006189555125725338</v>
+        <v>0.006382978723404255</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00909090909090909</v>
+        <v>0.009284332688588007</v>
       </c>
     </row>
     <row r="4">
@@ -87731,16 +87731,16 @@
         <v>2274</v>
       </c>
       <c r="C4" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D4" t="n">
-        <v>0.09315587455836727</v>
+        <v>0.03223935475404736</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02902374670184697</v>
+        <v>0.02858399296394019</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01276595744680851</v>
+        <v>0.01257253384912959</v>
       </c>
       <c r="G4" t="n">
         <v>0.0218568665377176</v>
@@ -87757,7 +87757,7 @@
         <v>125</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1503362893641561</v>
+        <v>0.05327114363462399</v>
       </c>
       <c r="E5" t="n">
         <v>0.05494505494505494</v>
@@ -87777,19 +87777,19 @@
         <v>2274</v>
       </c>
       <c r="C6" t="n">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2351372510889034</v>
+        <v>0.087537799542813</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08751099384344767</v>
+        <v>0.08927000879507475</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03849129593810445</v>
+        <v>0.03926499032882012</v>
       </c>
       <c r="G6" t="n">
-        <v>0.08452611218568665</v>
+        <v>0.08529980657640232</v>
       </c>
     </row>
     <row r="7">
@@ -87800,19 +87800,19 @@
         <v>2275</v>
       </c>
       <c r="C7" t="n">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3544192906816934</v>
+        <v>0.1438082653718702</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1375824175824176</v>
+        <v>0.1345054945054945</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06054158607350096</v>
+        <v>0.05918762088974855</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1450676982591876</v>
+        <v>0.1444874274661509</v>
       </c>
     </row>
     <row r="8">
@@ -87823,19 +87823,19 @@
         <v>2274</v>
       </c>
       <c r="C8" t="n">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5019164457691265</v>
+        <v>0.2319913254942476</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2304309586631486</v>
+        <v>0.2321899736147757</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1013539651837524</v>
+        <v>0.1021276595744681</v>
       </c>
       <c r="G8" t="n">
-        <v>0.24642166344294</v>
+        <v>0.246615087040619</v>
       </c>
     </row>
     <row r="9">
@@ -87846,16 +87846,16 @@
         <v>2275</v>
       </c>
       <c r="C9" t="n">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6575498726607941</v>
+        <v>0.3601595173984833</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3727472527472527</v>
+        <v>0.3723076923076923</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1640232108317215</v>
+        <v>0.1638297872340425</v>
       </c>
       <c r="G9" t="n">
         <v>0.4104448742746615</v>
@@ -87872,7 +87872,7 @@
         <v>1229</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7961568662280971</v>
+        <v>0.5276006793290601</v>
       </c>
       <c r="E10" t="n">
         <v>0.5404573438874231</v>
@@ -87895,7 +87895,7 @@
         <v>1819</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9402792999240394</v>
+        <v>0.8169178864923592</v>
       </c>
       <c r="E11" t="n">
         <v>0.7995604395604395</v>
@@ -87918,7 +87918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87984,6 +87984,16 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>train_selected_threshold</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>train_selected_threshold_f1</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
@@ -87996,7 +88006,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>logit_elasticnet_binned_ohe_balanced</t>
+          <t>logit_binned_ohe_balanced_calibrated</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -88010,30 +88020,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.8811585985239313</v>
+        <v>0.881130493247186</v>
       </c>
       <c r="F2" t="n">
-        <v>0.697863011313659</v>
+        <v>0.6980576057044253</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7936804073504355</v>
+        <v>0.8403330948442059</v>
       </c>
       <c r="H2" t="n">
-        <v>0.643112712468934</v>
+        <v>0.5876274656093299</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8771380317718289</v>
+        <v>0.8771122911143998</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6933499882637983</v>
+        <v>0.6933517849967762</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7898971247691902</v>
+        <v>0.8415105952694979</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6373226075738029</v>
-      </c>
-      <c r="M2" t="inlineStr">
+        <v>0.5938943336712853</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.3140000487021511</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.6546968514181629</v>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>Final model trained on full train split and scored on held-out test split.</t>
         </is>
@@ -88050,7 +88066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88398,38 +88414,38 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mean_regressor</t>
+          <t>classic_linear_boxcox_standard_scaler</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.0001604638596926389</v>
+        <v>0.04145249374348172</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001217442387676462</v>
+        <v>0.007168475934655649</v>
       </c>
       <c r="D9" t="n">
-        <v>84933.14754427197</v>
+        <v>66783.52904943706</v>
       </c>
       <c r="E9" t="n">
-        <v>1278.344049836328</v>
+        <v>1442.713056953945</v>
       </c>
       <c r="F9" t="n">
-        <v>17995185275.5386</v>
+        <v>17249943985.31007</v>
       </c>
       <c r="G9" t="n">
-        <v>1009063682.08735</v>
+        <v>1045989194.736032</v>
       </c>
       <c r="H9" t="n">
-        <v>235.0399495657002</v>
+        <v>176.2358685462974</v>
       </c>
       <c r="I9" t="n">
-        <v>53.88888012653806</v>
+        <v>34.26450162410745</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8829624687500001</v>
+        <v>0.6385819079931372</v>
       </c>
       <c r="K9" t="n">
-        <v>0.007611817593881241</v>
+        <v>0.007936602634370784</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -88438,38 +88454,38 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>classic_linear_log1p_standard_scaler</t>
+          <t>classic_linear_yeojohnson_standard_scaler</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.006259702724582939</v>
+        <v>0.04111772549426074</v>
       </c>
       <c r="C10" t="n">
-        <v>0.006291317323077628</v>
+        <v>0.007158612312357105</v>
       </c>
       <c r="D10" t="n">
-        <v>67677.63308910583</v>
+        <v>66786.57552616723</v>
       </c>
       <c r="E10" t="n">
-        <v>1481.333668683103</v>
+        <v>1442.597648231144</v>
       </c>
       <c r="F10" t="n">
-        <v>18107603645.34259</v>
+        <v>17255961149.74127</v>
       </c>
       <c r="G10" t="n">
-        <v>1075613382.374136</v>
+        <v>1046177246.333138</v>
       </c>
       <c r="H10" t="n">
-        <v>148.3383251387553</v>
+        <v>176.0697063962918</v>
       </c>
       <c r="I10" t="n">
-        <v>30.74054848418426</v>
+        <v>34.26276775408589</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6409103666562173</v>
+        <v>0.6383616556326095</v>
       </c>
       <c r="K10" t="n">
-        <v>0.006747934191879984</v>
+        <v>0.007864580475057014</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -88478,38 +88494,38 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>median_regressor</t>
+          <t>mean_regressor</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.1083769211496982</v>
+        <v>-0.0001604638596926389</v>
       </c>
       <c r="C11" t="n">
-        <v>0.002159443703462797</v>
+        <v>0.0001217442387676462</v>
       </c>
       <c r="D11" t="n">
-        <v>75011.173410296</v>
+        <v>84933.14754427197</v>
       </c>
       <c r="E11" t="n">
-        <v>1494.78183942886</v>
+        <v>1278.344049836328</v>
       </c>
       <c r="F11" t="n">
-        <v>19943194831.72226</v>
+        <v>17995185275.5386</v>
       </c>
       <c r="G11" t="n">
-        <v>1139733945.430216</v>
+        <v>1009063682.08735</v>
       </c>
       <c r="H11" t="n">
-        <v>124.7104595910728</v>
+        <v>235.0399495657002</v>
       </c>
       <c r="I11" t="n">
-        <v>28.44224996650644</v>
+        <v>53.88888012653806</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7462414725535839</v>
+        <v>0.8829624687500001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.008404322865485285</v>
+        <v>0.007611817593881241</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -88518,40 +88534,120 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>classic_linear_log1p_standard_scaler</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.006259702724582939</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.006291317323077628</v>
+      </c>
+      <c r="D12" t="n">
+        <v>67677.63308910583</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1481.333668683103</v>
+      </c>
+      <c r="F12" t="n">
+        <v>18107603645.34259</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1075613382.374136</v>
+      </c>
+      <c r="H12" t="n">
+        <v>148.3383251387553</v>
+      </c>
+      <c r="I12" t="n">
+        <v>30.74054848418426</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.6409103666562173</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.006747934191879984</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>median_regressor</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.1083769211496982</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.002159443703462797</v>
+      </c>
+      <c r="D13" t="n">
+        <v>75011.173410296</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1494.78183942886</v>
+      </c>
+      <c r="F13" t="n">
+        <v>19943194831.72226</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1139733945.430216</v>
+      </c>
+      <c r="H13" t="n">
+        <v>124.7104595910728</v>
+      </c>
+      <c r="I13" t="n">
+        <v>28.44224996650644</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.7462414725535839</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.008404322865485285</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>random_regressor</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B14" t="n">
         <v>-1.053439423531181</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C14" t="n">
         <v>0.0569242886524596</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D14" t="n">
         <v>115041.0624527173</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E14" t="n">
         <v>2091.856279170782</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F14" t="n">
         <v>36908630285.07372</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G14" t="n">
         <v>1368710206.121246</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H14" t="n">
         <v>164.0865786876999</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I14" t="n">
         <v>65.34359371801101</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J14" t="n">
         <v>0.903809739193137</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K14" t="n">
         <v>0.006508540706215832</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L14" t="n">
         <v>0</v>
       </c>
     </row>

--- a/slidedeck/data/model_slide_data.xlsx
+++ b/slidedeck/data/model_slide_data.xlsx
@@ -1028,7 +1028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1044,15 +1044,10 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>signed_coefficient</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
           <t>transformed_terms</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>importance_std</t>
         </is>
@@ -1061,190 +1056,240 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>categorical__Route To Market_Reseller</t>
+          <t>Route To Market</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2287913113832474</v>
+        <v>0.2967648208141327</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2287913113832474</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>categorical__Supplies Subgroup_Shelters &amp; RV</t>
+          <t>Supplies Subgroup</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09820764511823654</v>
+        <v>0.27311971783638</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09820764511823654</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>categorical__Route To Market_Telesales</t>
+          <t>Revenue From Client Past Two Years (USD)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05422118306159973</v>
+        <v>0.07112428545951843</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05422118306159973</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>numerical__Total Days Identified Through Qualified</t>
+          <t>Competitor Type</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05255987122654915</v>
+        <v>0.06434359401464462</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05255987122654915</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>categorical__Supplies Subgroup_Garage &amp; Car Care</t>
+          <t>Region</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05176772922277451</v>
+        <v>0.06157518923282623</v>
       </c>
       <c r="C6" t="n">
-        <v>0.05176772922277451</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>categorical__Supplies Subgroup_Motorcycle Parts</t>
+          <t>Total Days Identified Through Qualified</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04478615522384644</v>
+        <v>0.05255987122654915</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04478615522384644</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>categorical__Competitor Type_MISSING</t>
+          <t>Client Size By Revenue (USD)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03833722695708275</v>
+        <v>0.04760383442044258</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03833722695708275</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>categorical__Revenue From Client Past Two Years (USD)_0 - 25,000</t>
+          <t>Client Size By Employee Count</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02786984667181969</v>
+        <v>0.04526816308498383</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02786984667181969</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>categorical__Revenue From Client Past Two Years (USD)_More than 100,000</t>
+          <t>Supplies Group</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02700748480856419</v>
+        <v>0.01751848310232162</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02700748480856419</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>categorical__Supplies Subgroup_Replacement Parts</t>
+          <t>Elapsed Days In Sales Stage</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02689552120864391</v>
+        <v>0.01553967222571373</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02689552120864391</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ratio Days Identified To Total Days</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.0140520790591836</v>
+      </c>
+      <c r="C12" t="n">
         <v>1</v>
       </c>
-      <c r="E11" t="n">
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Days Identified Through Closing</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.01173211447894573</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ratio Days Validated To Total Days</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.01111062336713076</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sales Stage Change Count</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.009022132493555546</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ratio Days Qualified To Total Days</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.008665298111736774</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -86492,7 +86537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86533,15 +86578,35 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>precision_mean</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>precision_std</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>recall_mean</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>recall_std</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>f1_mean</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>f1_std</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>n_failed</t>
         </is>
@@ -86572,12 +86637,24 @@
         <v>0.005891976215397637</v>
       </c>
       <c r="H2" t="n">
+        <v>0.6269140050499862</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.01131547974546328</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.810131034288428</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.006975526899547858</v>
+      </c>
+      <c r="L2" t="n">
         <v>0.7068293562382115</v>
       </c>
-      <c r="I2" t="n">
+      <c r="M2" t="n">
         <v>0.009790777061447854</v>
       </c>
-      <c r="J2" t="n">
+      <c r="N2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -86606,12 +86683,24 @@
         <v>0.005416385756810691</v>
       </c>
       <c r="H3" t="n">
+        <v>0.58782909096241</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.009567443909138844</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.8385701345462218</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.004374874500207381</v>
+      </c>
+      <c r="L3" t="n">
         <v>0.6911286780642751</v>
       </c>
-      <c r="I3" t="n">
+      <c r="M3" t="n">
         <v>0.007225987703506406</v>
       </c>
-      <c r="J3" t="n">
+      <c r="N3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -86640,12 +86729,24 @@
         <v>0.002882573554126725</v>
       </c>
       <c r="H4" t="n">
+        <v>0.7763101530423991</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.008081353391280693</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6087382193879339</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.01125925573472648</v>
+      </c>
+      <c r="L4" t="n">
         <v>0.6823398309631026</v>
       </c>
-      <c r="I4" t="n">
+      <c r="M4" t="n">
         <v>0.008407140022573497</v>
       </c>
-      <c r="J4" t="n">
+      <c r="N4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -86674,12 +86775,24 @@
         <v>0.007895207356770791</v>
       </c>
       <c r="H5" t="n">
+        <v>0.5299742035267634</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.01168668866481574</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.817759352154822</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.007653141302854197</v>
+      </c>
+      <c r="L5" t="n">
         <v>0.643112712468934</v>
       </c>
-      <c r="I5" t="n">
+      <c r="M5" t="n">
         <v>0.01065785074699211</v>
       </c>
-      <c r="J5" t="n">
+      <c r="N5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -86708,12 +86821,24 @@
         <v>0.007635615319973337</v>
       </c>
       <c r="H6" t="n">
+        <v>0.5300480731232893</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.01132393851248348</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.817759352154822</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.007869077870088134</v>
+      </c>
+      <c r="L6" t="n">
         <v>0.643169280418737</v>
       </c>
-      <c r="I6" t="n">
+      <c r="M6" t="n">
         <v>0.01041661405314055</v>
       </c>
-      <c r="J6" t="n">
+      <c r="N6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -86742,12 +86867,24 @@
         <v>0.002963045688369091</v>
       </c>
       <c r="H7" t="n">
+        <v>0.7111746540752869</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.006902739266586057</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5007047577418887</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.01202107305064498</v>
+      </c>
+      <c r="L7" t="n">
         <v>0.5876274656093299</v>
       </c>
-      <c r="I7" t="n">
+      <c r="M7" t="n">
         <v>0.01020369228274071</v>
       </c>
-      <c r="J7" t="n">
+      <c r="N7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -86776,12 +86913,24 @@
         <v>0.003374486507193572</v>
       </c>
       <c r="H8" t="n">
+        <v>0.7108721305626722</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.008712052271902962</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5131418126936804</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.01331058829753436</v>
+      </c>
+      <c r="L8" t="n">
         <v>0.5959828291514137</v>
       </c>
-      <c r="I8" t="n">
+      <c r="M8" t="n">
         <v>0.01093835291011654</v>
       </c>
-      <c r="J8" t="n">
+      <c r="N8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -86810,12 +86959,24 @@
         <v>0.003073224702100414</v>
       </c>
       <c r="H9" t="n">
+        <v>0.7125897899704303</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.00816064576127834</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.5098253380149947</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01212448308129676</v>
+      </c>
+      <c r="L9" t="n">
         <v>0.5943442370054564</v>
       </c>
-      <c r="I9" t="n">
+      <c r="M9" t="n">
         <v>0.009979210756378148</v>
       </c>
-      <c r="J9" t="n">
+      <c r="N9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -86844,12 +87005,24 @@
         <v>0.005722608230804933</v>
       </c>
       <c r="H10" t="n">
+        <v>0.5243023863756335</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.008539626904805182</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.8085565404088826</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.006059201965162753</v>
+      </c>
+      <c r="L10" t="n">
         <v>0.6360934863488088</v>
       </c>
-      <c r="I10" t="n">
+      <c r="M10" t="n">
         <v>0.007341581998092306</v>
       </c>
-      <c r="J10" t="n">
+      <c r="N10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -86878,12 +87051,24 @@
         <v>0.002414774515868585</v>
       </c>
       <c r="H11" t="n">
+        <v>0.7167030676574802</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.008626451904090178</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.473261507079879</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01102548890008316</v>
+      </c>
+      <c r="L11" t="n">
         <v>0.5700107706623559</v>
       </c>
-      <c r="I11" t="n">
+      <c r="M11" t="n">
         <v>0.008637340913124606</v>
       </c>
-      <c r="J11" t="n">
+      <c r="N11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -86912,12 +87097,24 @@
         <v>0.002470388242247739</v>
       </c>
       <c r="H12" t="n">
+        <v>0.7162381448730094</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.009761304644855832</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4729297633946581</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0107632093123463</v>
+      </c>
+      <c r="L12" t="n">
         <v>0.5696159324654674</v>
       </c>
-      <c r="I12" t="n">
+      <c r="M12" t="n">
         <v>0.008343765434171466</v>
       </c>
-      <c r="J12" t="n">
+      <c r="N12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -86946,12 +87143,24 @@
         <v>0.007059674046021744</v>
       </c>
       <c r="H13" t="n">
+        <v>0.5204537102469808</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.01025794161469152</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.7957050635756155</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.01105879664650136</v>
+      </c>
+      <c r="L13" t="n">
         <v>0.6292835523135512</v>
       </c>
-      <c r="I13" t="n">
+      <c r="M13" t="n">
         <v>0.01061365046270664</v>
       </c>
-      <c r="J13" t="n">
+      <c r="N13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -86980,12 +87189,24 @@
         <v>0.002082293169188209</v>
       </c>
       <c r="H14" t="n">
+        <v>0.6843062922460865</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.006041007482650775</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.4548537530609146</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.01057163743379905</v>
+      </c>
+      <c r="L14" t="n">
         <v>0.5464187873581289</v>
       </c>
-      <c r="I14" t="n">
+      <c r="M14" t="n">
         <v>0.008389729914154242</v>
       </c>
-      <c r="J14" t="n">
+      <c r="N14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -87014,12 +87235,24 @@
         <v>0.001986574841447083</v>
       </c>
       <c r="H15" t="n">
+        <v>0.6842941667433381</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.005884323395802298</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.4553512654987255</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.01054622802916655</v>
+      </c>
+      <c r="L15" t="n">
         <v>0.5467708451685505</v>
       </c>
-      <c r="I15" t="n">
+      <c r="M15" t="n">
         <v>0.008200986880072232</v>
       </c>
-      <c r="J15" t="n">
+      <c r="N15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -87048,12 +87281,24 @@
         <v>0.00121384248121297</v>
       </c>
       <c r="H16" t="n">
+        <v>0.2302047781569966</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.002725037444141857</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.2236963407853673</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.002661475279300156</v>
+      </c>
+      <c r="L16" t="n">
         <v>0.2269038960423601</v>
       </c>
-      <c r="I16" t="n">
+      <c r="M16" t="n">
         <v>0.002692826940019715</v>
       </c>
-      <c r="J16" t="n">
+      <c r="N16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -87082,12 +87327,24 @@
         <v>3.884716467977554e-05</v>
       </c>
       <c r="H17" t="n">
+        <v>0.2272530286210917</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.884716467977554e-05</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>0.3703442118613253</v>
       </c>
-      <c r="I17" t="n">
+      <c r="M17" t="n">
         <v>5.158293634861289e-05</v>
       </c>
-      <c r="J17" t="n">
+      <c r="N17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -87102,7 +87359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87143,15 +87400,35 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>precision_mean</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>precision_std</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>recall_mean</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>recall_std</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>f1_mean</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>f1_std</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>n_failed</t>
         </is>
@@ -87182,12 +87459,24 @@
         <v>0.002963045688369091</v>
       </c>
       <c r="H2" t="n">
+        <v>0.7111746540752869</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.006902739266586057</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5007047577418887</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.01202107305064498</v>
+      </c>
+      <c r="L2" t="n">
         <v>0.5876274656093299</v>
       </c>
-      <c r="I2" t="n">
+      <c r="M2" t="n">
         <v>0.01020369228274071</v>
       </c>
-      <c r="J2" t="n">
+      <c r="N2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -87202,7 +87491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87243,15 +87532,35 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>precision_mean</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>precision_std</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>recall_mean</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>recall_std</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>f1_mean</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>f1_std</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>n_failed</t>
         </is>
@@ -87282,12 +87591,24 @@
         <v>0.00121384248121297</v>
       </c>
       <c r="H2" t="n">
+        <v>0.2302047781569966</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.002725037444141857</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.2236963407853673</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.002661475279300156</v>
+      </c>
+      <c r="L2" t="n">
         <v>0.2269038960423601</v>
       </c>
-      <c r="I2" t="n">
+      <c r="M2" t="n">
         <v>0.002692826940019715</v>
       </c>
-      <c r="J2" t="n">
+      <c r="N2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -87440,7 +87761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87456,15 +87777,10 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>signed_coefficient</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
           <t>transformed_terms</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>importance_std</t>
         </is>
@@ -87473,190 +87789,240 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Supplies Group</t>
+          <t>Total Days Identified Through Qualified</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>18.37140037857071</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Supplies Subgroup</t>
+          <t>Total Days Identified Through Closing</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>4.848827133938185</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Region</t>
+          <t>Sales Stage Change Count</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>4.40194130932298</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Route To Market</t>
+          <t>Ratio Days Identified To Total Days</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>2.928201903799787</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Elapsed Days In Sales Stage</t>
+          <t>Ratio Days Validated To Total Days</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>2.502431839302863</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sales Stage Change Count</t>
+          <t>Revenue From Client Past Two Years (USD)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>2.267601509817701</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total Days Identified Through Closing</t>
+          <t>Supplies Subgroup</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1.706140194977952</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Total Days Identified Through Qualified</t>
+          <t>Elapsed Days In Sales Stage</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1.491084059133039</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Client Size By Revenue (USD)</t>
+          <t>Route To Market</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1.052739893119325</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.8555521112650204</v>
+      </c>
+      <c r="C11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ratio Days Qualified To Total Days</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.8520207303758971</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Competitor Type</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.6767353915149377</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Client Size By Employee Count</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B14" t="n">
+        <v>0.4401221613703557</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="C11" t="n">
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Client Size By Revenue (USD)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.3283870907104205</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="D11" t="n">
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Supplies Group</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.09199622216369947</v>
+      </c>
+      <c r="C16" t="n">
         <v>1</v>
       </c>
-      <c r="E11" t="n">
+      <c r="D16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -87952,7 +88318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88023,10 +88389,25 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>train_selected_threshold_accuracy</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>train_selected_threshold_precision</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>train_selected_threshold_recall</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>train_selected_threshold_f1</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -88081,9 +88462,18 @@
         <v>0.3140000487021511</v>
       </c>
       <c r="N2" t="n">
+        <v>0.8249769185838374</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.5933962264150944</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.7301218804410912</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0.6546968514181629</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Final model trained on full train split and scored on held-out test split.</t>
         </is>
@@ -88516,10 +88906,10 @@
         <v>65.3964681733629</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7550502953367538</v>
+        <v>0.7550502953367539</v>
       </c>
       <c r="K10" t="n">
-        <v>0.007765429060309128</v>
+        <v>0.007765429060309091</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>

--- a/slidedeck/data/model_slide_data.xlsx
+++ b/slidedeck/data/model_slide_data.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Selected model: logit_binned_ohe_balanced_calibrated | Baseline: random_classifier</t>
+          <t>Selected model: random_forest_classifier_balanced | Baseline: random_classifier</t>
         </is>
       </c>
     </row>
@@ -86537,7 +86537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86619,40 +86619,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9140224688816492</v>
+        <v>0.9166263168114168</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004096515051063659</v>
+        <v>0.003872988600675628</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7727977418390275</v>
+        <v>0.7839932418273847</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01129734405204536</v>
+        <v>0.008734272456820515</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8472481097273652</v>
+        <v>0.872025280380049</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005891976215397637</v>
+        <v>0.002396041169168135</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6269140050499862</v>
+        <v>0.7780935086023624</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01131547974546328</v>
+        <v>0.006833173590338825</v>
       </c>
       <c r="J2" t="n">
-        <v>0.810131034288428</v>
+        <v>0.6112255753969482</v>
       </c>
       <c r="K2" t="n">
-        <v>0.006975526899547858</v>
+        <v>0.01110534936184623</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7068293562382115</v>
+        <v>0.6845835769255423</v>
       </c>
       <c r="M2" t="n">
-        <v>0.009790777061447854</v>
+        <v>0.007557192019724195</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -86661,44 +86661,44 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>xgboost_balanced</t>
+          <t>random_forest_classifier_balanced</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9123912353315229</v>
+        <v>0.9140224688816492</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003497478880795551</v>
+        <v>0.004096515051063659</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7834938339761315</v>
+        <v>0.7727977418390275</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006874214727794301</v>
+        <v>0.01129734405204536</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8296308779426493</v>
+        <v>0.8472481097273652</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005416385756810691</v>
+        <v>0.005891976215397637</v>
       </c>
       <c r="H3" t="n">
-        <v>0.58782909096241</v>
+        <v>0.6269140050499862</v>
       </c>
       <c r="I3" t="n">
-        <v>0.009567443909138844</v>
+        <v>0.01131547974546328</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8385701345462218</v>
+        <v>0.810131034288428</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004374874500207381</v>
+        <v>0.006975526899547858</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6911286780642751</v>
+        <v>0.7068293562382115</v>
       </c>
       <c r="M3" t="n">
-        <v>0.007225987703506406</v>
+        <v>0.009790777061447854</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -86707,44 +86707,44 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>xgboost</t>
+          <t>xgboost_balanced</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9123864805636017</v>
+        <v>0.9123912353315229</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003481238918302272</v>
+        <v>0.003497478880795551</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7863944206132294</v>
+        <v>0.7834938339761315</v>
       </c>
       <c r="E4" t="n">
-        <v>0.005723900679462718</v>
+        <v>0.006874214727794301</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8712150847967752</v>
+        <v>0.8296308779426493</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002882573554126725</v>
+        <v>0.005416385756810691</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7763101530423991</v>
+        <v>0.58782909096241</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008081353391280693</v>
+        <v>0.009567443909138844</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6087382193879339</v>
+        <v>0.8385701345462218</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01125925573472648</v>
+        <v>0.004374874500207381</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6823398309631026</v>
+        <v>0.6911286780642751</v>
       </c>
       <c r="M4" t="n">
-        <v>0.008407140022573497</v>
+        <v>0.007225987703506406</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -86753,44 +86753,44 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>logit_elasticnet_binned_ohe_balanced</t>
+          <t>xgboost</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8811585985239313</v>
+        <v>0.9123864805636017</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004389213114772924</v>
+        <v>0.003481238918302272</v>
       </c>
       <c r="D5" t="n">
-        <v>0.697863011313659</v>
+        <v>0.7863944206132294</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005226812006440109</v>
+        <v>0.005723900679462718</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7936804073504355</v>
+        <v>0.8712150847967752</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007895207356770791</v>
+        <v>0.002882573554126725</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5299742035267634</v>
+        <v>0.7763101530423991</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01168668866481574</v>
+        <v>0.008081353391280693</v>
       </c>
       <c r="J5" t="n">
-        <v>0.817759352154822</v>
+        <v>0.6087382193879339</v>
       </c>
       <c r="K5" t="n">
-        <v>0.007653141302854197</v>
+        <v>0.01125925573472648</v>
       </c>
       <c r="L5" t="n">
-        <v>0.643112712468934</v>
+        <v>0.6823398309631026</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01065785074699211</v>
+        <v>0.008407140022573497</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -86799,44 +86799,44 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>logit_binned_ohe_balanced</t>
+          <t>logit_elasticnet_binned_ohe_balanced</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8811365072867504</v>
+        <v>0.8811585985239313</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004376531559578211</v>
+        <v>0.004389213114772924</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6979843583264473</v>
+        <v>0.697863011313659</v>
       </c>
       <c r="E6" t="n">
-        <v>0.005228907087311024</v>
+        <v>0.005226812006440109</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7937369346877954</v>
+        <v>0.7936804073504355</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007635615319973337</v>
+        <v>0.007895207356770791</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5300480731232893</v>
+        <v>0.5299742035267634</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01132393851248348</v>
+        <v>0.01168668866481574</v>
       </c>
       <c r="J6" t="n">
         <v>0.817759352154822</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007869077870088134</v>
+        <v>0.007653141302854197</v>
       </c>
       <c r="L6" t="n">
-        <v>0.643169280418737</v>
+        <v>0.643112712468934</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01041661405314055</v>
+        <v>0.01065785074699211</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -86845,44 +86845,44 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>logit_binned_ohe_balanced_calibrated</t>
+          <t>logit_binned_ohe_balanced</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.881130493247186</v>
+        <v>0.8811365072867504</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004370391028659821</v>
+        <v>0.004376531559578211</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6980576057044253</v>
+        <v>0.6979843583264473</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005206617861945132</v>
+        <v>0.005228907087311024</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8403330948442059</v>
+        <v>0.7937369346877954</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002963045688369091</v>
+        <v>0.007635615319973337</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7111746540752869</v>
+        <v>0.5300480731232893</v>
       </c>
       <c r="I7" t="n">
-        <v>0.006902739266586057</v>
+        <v>0.01132393851248348</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5007047577418887</v>
+        <v>0.817759352154822</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01202107305064498</v>
+        <v>0.007869077870088134</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5876274656093299</v>
+        <v>0.643169280418737</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01020369228274071</v>
+        <v>0.01041661405314055</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -86891,44 +86891,44 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>logit_binned_ohe</t>
+          <t>logit_binned_ohe_balanced_calibrated</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8810525664936373</v>
+        <v>0.881130493247186</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004399871941074101</v>
+        <v>0.004370391028659821</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7000061433590246</v>
+        <v>0.6980576057044253</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005493287863198479</v>
+        <v>0.005206617861945132</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8419347122034452</v>
+        <v>0.8403330948442059</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003374486507193572</v>
+        <v>0.002963045688369091</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7108721305626722</v>
+        <v>0.7111746540752869</v>
       </c>
       <c r="I8" t="n">
-        <v>0.008712052271902962</v>
+        <v>0.006902739266586057</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5131418126936804</v>
+        <v>0.5007047577418887</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01331058829753436</v>
+        <v>0.01202107305064498</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5959828291514137</v>
+        <v>0.5876274656093299</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01093835291011654</v>
+        <v>0.01020369228274071</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -86937,44 +86937,44 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>logit_elasticnet_binned_ohe</t>
+          <t>logit_binned_ohe</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8810395947267043</v>
+        <v>0.8810525664936373</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004397931763937513</v>
+        <v>0.004399871941074101</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7001044823040902</v>
+        <v>0.7000061433590246</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005480282425292697</v>
+        <v>0.005493287863198479</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8418781848660852</v>
+        <v>0.8419347122034452</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003073224702100414</v>
+        <v>0.003374486507193572</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7125897899704303</v>
+        <v>0.7108721305626722</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00816064576127834</v>
+        <v>0.008712052271902962</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5098253380149947</v>
+        <v>0.5131418126936804</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01212448308129676</v>
+        <v>0.01331058829753436</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5943442370054564</v>
+        <v>0.5959828291514137</v>
       </c>
       <c r="M9" t="n">
-        <v>0.009979210756378148</v>
+        <v>0.01093835291011654</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -86983,44 +86983,44 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>logit_elastic_binned_woe_balanced</t>
+          <t>logit_elasticnet_binned_ohe</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8772949445020284</v>
+        <v>0.8810395947267043</v>
       </c>
       <c r="C10" t="n">
-        <v>0.003761449015753651</v>
+        <v>0.004397931763937513</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6915303944720554</v>
+        <v>0.7001044823040902</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003401032940688927</v>
+        <v>0.005480282425292697</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7897235878172972</v>
+        <v>0.8418781848660852</v>
       </c>
       <c r="G10" t="n">
-        <v>0.005722608230804933</v>
+        <v>0.003073224702100414</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5243023863756335</v>
+        <v>0.7125897899704303</v>
       </c>
       <c r="I10" t="n">
-        <v>0.008539626904805182</v>
+        <v>0.00816064576127834</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8085565404088826</v>
+        <v>0.5098253380149947</v>
       </c>
       <c r="K10" t="n">
-        <v>0.006059201965162753</v>
+        <v>0.01212448308129676</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6360934863488088</v>
+        <v>0.5943442370054564</v>
       </c>
       <c r="M10" t="n">
-        <v>0.007341581998092306</v>
+        <v>0.009979210756378148</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -87029,44 +87029,44 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>logit_elastic_binned_woe</t>
+          <t>logit_elastic_binned_woe_balanced</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8771585297862465</v>
+        <v>0.8772949445020284</v>
       </c>
       <c r="C11" t="n">
-        <v>0.003848776251252489</v>
+        <v>0.003761449015753651</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6930046960949421</v>
+        <v>0.6915303944720554</v>
       </c>
       <c r="E11" t="n">
-        <v>0.003656414022245295</v>
+        <v>0.003401032940688927</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8377705642287078</v>
+        <v>0.7897235878172972</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002414774515868585</v>
+        <v>0.005722608230804933</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7167030676574802</v>
+        <v>0.5243023863756335</v>
       </c>
       <c r="I11" t="n">
-        <v>0.008626451904090178</v>
+        <v>0.008539626904805182</v>
       </c>
       <c r="J11" t="n">
-        <v>0.473261507079879</v>
+        <v>0.8085565404088826</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01102548890008316</v>
+        <v>0.006059201965162753</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5700107706623559</v>
+        <v>0.6360934863488088</v>
       </c>
       <c r="M11" t="n">
-        <v>0.008637340913124606</v>
+        <v>0.007341581998092306</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -87075,44 +87075,44 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>logit_binned_woe</t>
+          <t>logit_elastic_binned_woe</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8771509619122287</v>
+        <v>0.8771585297862465</v>
       </c>
       <c r="C12" t="n">
-        <v>0.003836771048671129</v>
+        <v>0.003848776251252489</v>
       </c>
       <c r="D12" t="n">
-        <v>0.69300001724452</v>
+        <v>0.6930046960949421</v>
       </c>
       <c r="E12" t="n">
-        <v>0.003681078766040902</v>
+        <v>0.003656414022245295</v>
       </c>
       <c r="F12" t="n">
-        <v>0.837619832354658</v>
+        <v>0.8377705642287078</v>
       </c>
       <c r="G12" t="n">
-        <v>0.002470388242247739</v>
+        <v>0.002414774515868585</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7162381448730094</v>
+        <v>0.7167030676574802</v>
       </c>
       <c r="I12" t="n">
-        <v>0.009761304644855832</v>
+        <v>0.008626451904090178</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4729297633946581</v>
+        <v>0.473261507079879</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0107632093123463</v>
+        <v>0.01102548890008316</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5696159324654674</v>
+        <v>0.5700107706623559</v>
       </c>
       <c r="M12" t="n">
-        <v>0.008343765434171466</v>
+        <v>0.008637340913124606</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -87121,44 +87121,44 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>logit_elasticnet_robust_scaler_balanced</t>
+          <t>logit_binned_woe</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.867810003520171</v>
+        <v>0.8771509619122287</v>
       </c>
       <c r="C13" t="n">
-        <v>0.005528704925116762</v>
+        <v>0.003836771048671129</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6694910817508173</v>
+        <v>0.69300001724452</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01112195718805921</v>
+        <v>0.003681078766040902</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7869163213810961</v>
+        <v>0.837619832354658</v>
       </c>
       <c r="G13" t="n">
-        <v>0.007059674046021744</v>
+        <v>0.002470388242247739</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5204537102469808</v>
+        <v>0.7162381448730094</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01025794161469152</v>
+        <v>0.009761304644855832</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7957050635756155</v>
+        <v>0.4729297633946581</v>
       </c>
       <c r="K13" t="n">
-        <v>0.01105879664650136</v>
+        <v>0.0107632093123463</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6292835523135512</v>
+        <v>0.5696159324654674</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01061365046270664</v>
+        <v>0.008343765434171466</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -87167,44 +87167,44 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>logit_elasticnet_robust_scaler</t>
+          <t>logit_elasticnet_robust_scaler_balanced</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.867526389543505</v>
+        <v>0.867810003520171</v>
       </c>
       <c r="C14" t="n">
-        <v>0.005529273069482899</v>
+        <v>0.005528704925116762</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6745461453118697</v>
+        <v>0.6694910817508173</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01096817627836946</v>
+        <v>0.01112195718805921</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8284249714713926</v>
+        <v>0.7869163213810961</v>
       </c>
       <c r="G14" t="n">
-        <v>0.002082293169188209</v>
+        <v>0.007059674046021744</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6843062922460865</v>
+        <v>0.5204537102469808</v>
       </c>
       <c r="I14" t="n">
-        <v>0.006041007482650775</v>
+        <v>0.01025794161469152</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4548537530609146</v>
+        <v>0.7957050635756155</v>
       </c>
       <c r="K14" t="n">
-        <v>0.01057163743379905</v>
+        <v>0.01105879664650136</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5464187873581289</v>
+        <v>0.6292835523135512</v>
       </c>
       <c r="M14" t="n">
-        <v>0.008389729914154242</v>
+        <v>0.01061365046270664</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -87213,44 +87213,44 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>classic_logit_robust_scaler</t>
+          <t>logit_elasticnet_robust_scaler</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8675160644922242</v>
+        <v>0.867526389543505</v>
       </c>
       <c r="C15" t="n">
-        <v>0.005518549551175742</v>
+        <v>0.005529273069482899</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6745771081576786</v>
+        <v>0.6745461453118697</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01097031333685288</v>
+        <v>0.01096817627836946</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8284814970336194</v>
+        <v>0.8284249714713926</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001986574841447083</v>
+        <v>0.002082293169188209</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6842941667433381</v>
+        <v>0.6843062922460865</v>
       </c>
       <c r="I15" t="n">
-        <v>0.005884323395802298</v>
+        <v>0.006041007482650775</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4553512654987255</v>
+        <v>0.4548537530609146</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01054622802916655</v>
+        <v>0.01057163743379905</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5467708451685505</v>
+        <v>0.5464187873581289</v>
       </c>
       <c r="M15" t="n">
-        <v>0.008200986880072232</v>
+        <v>0.008389729914154242</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -87259,44 +87259,44 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>random_classifier</t>
+          <t>classic_logit_robust_scaler</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5018559714056471</v>
+        <v>0.8675160644922242</v>
       </c>
       <c r="C16" t="n">
-        <v>0.001720555585391747</v>
+        <v>0.005518549551175742</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2279191500425641</v>
+        <v>0.6745771081576786</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0006133047160225449</v>
+        <v>0.01097031333685288</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6535903477494552</v>
+        <v>0.8284814970336194</v>
       </c>
       <c r="G16" t="n">
-        <v>0.00121384248121297</v>
+        <v>0.001986574841447083</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2302047781569966</v>
+        <v>0.6842941667433381</v>
       </c>
       <c r="I16" t="n">
-        <v>0.002725037444141857</v>
+        <v>0.005884323395802298</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2236963407853673</v>
+        <v>0.4553512654987255</v>
       </c>
       <c r="K16" t="n">
-        <v>0.002661475279300156</v>
+        <v>0.01054622802916655</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2269038960423601</v>
+        <v>0.5467708451685505</v>
       </c>
       <c r="M16" t="n">
-        <v>0.002692826940019715</v>
+        <v>0.008200986880072232</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -87305,46 +87305,92 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>random_classifier</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.5018559714056471</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.001720555585391747</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.2279191500425641</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.0006133047160225449</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.6535903477494552</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.00121384248121297</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.2302047781569966</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.002725037444141857</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.2236963407853673</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.002661475279300156</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.2269038960423601</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.002692826940019715</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>always_true_classifier</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B18" t="n">
         <v>0.5</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C18" t="n">
         <v>0</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D18" t="n">
         <v>0.2272530286210917</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E18" t="n">
         <v>3.884716467977554e-05</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F18" t="n">
         <v>0.2272530286210917</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G18" t="n">
         <v>3.884716467977554e-05</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H18" t="n">
         <v>0.2272530286210917</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I18" t="n">
         <v>3.884716467977554e-05</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L18" t="n">
         <v>0.3703442118613253</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M18" t="n">
         <v>5.158293634861289e-05</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -87437,44 +87483,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>logit_binned_ohe_balanced_calibrated</t>
+          <t>random_forest_classifier_balanced</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.881130493247186</v>
+        <v>0.9140224688816492</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004370391028659821</v>
+        <v>0.004096515051063659</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6980576057044253</v>
+        <v>0.7727977418390275</v>
       </c>
       <c r="E2" t="n">
-        <v>0.005206617861945132</v>
+        <v>0.01129734405204536</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8403330948442059</v>
+        <v>0.8472481097273652</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002963045688369091</v>
+        <v>0.005891976215397637</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7111746540752869</v>
+        <v>0.6269140050499862</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006902739266586057</v>
+        <v>0.01131547974546328</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5007047577418887</v>
+        <v>0.810131034288428</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01202107305064498</v>
+        <v>0.006975526899547858</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5876274656093299</v>
+        <v>0.7068293562382115</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01020369228274071</v>
+        <v>0.009790777061447854</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -87681,7 +87727,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>logit_binned_ohe_balanced_calibrated</t>
+          <t>random_forest_classifier_balanced</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -87690,25 +87736,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8771122911143998</v>
+        <v>0.9116048160891104</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6933517849967762</v>
+        <v>0.7693212731610033</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8415105952694979</v>
+        <v>0.8614261848237053</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5938943336712853</v>
+        <v>0.7076066790352504</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7110871324521176</v>
+        <v>0.6798573975044563</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5098646034816248</v>
+        <v>0.7377176015473887</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5</v>
+        <v>0.5806481666978933</v>
       </c>
       <c r="J2" t="n">
         <v>22746</v>
@@ -87793,10 +87839,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.37140037857071</v>
+        <v>0.1741358393978058</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -87809,10 +87855,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.848827133938185</v>
+        <v>0.1461279336467704</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -87821,14 +87867,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sales Stage Change Count</t>
+          <t>Ratio Days Qualified To Total Days</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.40194130932298</v>
+        <v>0.09811580318990407</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -87837,14 +87883,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ratio Days Identified To Total Days</t>
+          <t>Sales Stage Change Count</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.928201903799787</v>
+        <v>0.09531998536472823</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -87853,14 +87899,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ratio Days Validated To Total Days</t>
+          <t>Revenue From Client Past Two Years (USD)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.502431839302863</v>
+        <v>0.09313218691299484</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -87869,11 +87915,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Revenue From Client Past Two Years (USD)</t>
+          <t>Ratio Days Identified To Total Days</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.267601509817701</v>
+        <v>0.08197809041557944</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -87885,14 +87931,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Supplies Subgroup</t>
+          <t>Elapsed Days In Sales Stage</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.706140194977952</v>
+        <v>0.0800428785162902</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -87901,14 +87947,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Elapsed Days In Sales Stage</t>
+          <t>Ratio Days Validated To Total Days</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.491084059133039</v>
+        <v>0.073859846596819</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -87921,10 +87967,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.052739893119325</v>
+        <v>0.04568964660543632</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -87937,7 +87983,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8555521112650204</v>
+        <v>0.03468392733196007</v>
       </c>
       <c r="C11" t="n">
         <v>6</v>
@@ -87949,14 +87995,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ratio Days Qualified To Total Days</t>
+          <t>Supplies Subgroup</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8520207303758971</v>
+        <v>0.03153107686010778</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -87969,7 +88015,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6767353915149377</v>
+        <v>0.0189935185618011</v>
       </c>
       <c r="C13" t="n">
         <v>2</v>
@@ -87985,7 +88031,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4401221613703557</v>
+        <v>0.01235550098241272</v>
       </c>
       <c r="C14" t="n">
         <v>4</v>
@@ -88001,10 +88047,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3283870907104205</v>
+        <v>0.007604936826221313</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -88017,10 +88063,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.09199622216369947</v>
+        <v>0.00642882879116884</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -88085,19 +88131,19 @@
         <v>2275</v>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.006657620624347824</v>
+        <v>0.01414954902385034</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006593406593406593</v>
+        <v>0.002637362637362637</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002901353965183753</v>
+        <v>0.001160541586073501</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002901353965183753</v>
+        <v>0.001160541586073501</v>
       </c>
     </row>
     <row r="3">
@@ -88108,19 +88154,19 @@
         <v>2275</v>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01749794825832251</v>
+        <v>0.03513692952501519</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01450549450549451</v>
+        <v>0.007912087912087912</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006382978723404255</v>
+        <v>0.003481624758220503</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009284332688588007</v>
+        <v>0.004642166344294004</v>
       </c>
     </row>
     <row r="4">
@@ -88131,19 +88177,19 @@
         <v>2274</v>
       </c>
       <c r="C4" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03223935475404736</v>
+        <v>0.06563938808025802</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02858399296394019</v>
+        <v>0.01715039577836412</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01257253384912959</v>
+        <v>0.007543520309477757</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0218568665377176</v>
+        <v>0.01218568665377176</v>
       </c>
     </row>
     <row r="5">
@@ -88154,19 +88200,19 @@
         <v>2275</v>
       </c>
       <c r="C5" t="n">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05327114363462399</v>
+        <v>0.112815668938653</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05494505494505494</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0241779497098646</v>
+        <v>0.01257253384912959</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0460348162475822</v>
+        <v>0.02475822050290135</v>
       </c>
     </row>
     <row r="6">
@@ -88177,19 +88223,19 @@
         <v>2274</v>
       </c>
       <c r="C6" t="n">
-        <v>203</v>
+        <v>163</v>
       </c>
       <c r="D6" t="n">
-        <v>0.087537799542813</v>
+        <v>0.1834857245203665</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08927000879507475</v>
+        <v>0.07167985927880387</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03926499032882012</v>
+        <v>0.03152804642166344</v>
       </c>
       <c r="G6" t="n">
-        <v>0.08529980657640232</v>
+        <v>0.0562862669245648</v>
       </c>
     </row>
     <row r="7">
@@ -88200,19 +88246,19 @@
         <v>2275</v>
       </c>
       <c r="C7" t="n">
-        <v>306</v>
+        <v>223</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1438082653718702</v>
+        <v>0.2787608390295248</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1345054945054945</v>
+        <v>0.09802197802197803</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05918762088974855</v>
+        <v>0.04313346228239845</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1444874274661509</v>
+        <v>0.09941972920696325</v>
       </c>
     </row>
     <row r="8">
@@ -88223,19 +88269,19 @@
         <v>2274</v>
       </c>
       <c r="C8" t="n">
-        <v>528</v>
+        <v>456</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2319913254942476</v>
+        <v>0.4110668124390828</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2321899736147757</v>
+        <v>0.2005277044854881</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1021276595744681</v>
+        <v>0.08820116054158607</v>
       </c>
       <c r="G8" t="n">
-        <v>0.246615087040619</v>
+        <v>0.1876208897485493</v>
       </c>
     </row>
     <row r="9">
@@ -88246,19 +88292,19 @@
         <v>2275</v>
       </c>
       <c r="C9" t="n">
-        <v>847</v>
+        <v>820</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3601595173984833</v>
+        <v>0.5738417493690567</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3723076923076923</v>
+        <v>0.3604395604395604</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1638297872340425</v>
+        <v>0.1586073500967118</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4104448742746615</v>
+        <v>0.3462282398452611</v>
       </c>
     </row>
     <row r="10">
@@ -88269,19 +88315,19 @@
         <v>2274</v>
       </c>
       <c r="C10" t="n">
-        <v>1229</v>
+        <v>1420</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5276006793290601</v>
+        <v>0.7392865038088421</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5404573438874231</v>
+        <v>0.6244503078276166</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2377176015473888</v>
+        <v>0.2746615087040619</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6481624758220502</v>
+        <v>0.620889748549323</v>
       </c>
     </row>
     <row r="11">
@@ -88292,16 +88338,16 @@
         <v>2275</v>
       </c>
       <c r="C11" t="n">
-        <v>1819</v>
+        <v>1960</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8169178864923592</v>
+        <v>0.8871508979032245</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7995604395604395</v>
+        <v>0.8615384615384616</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3518375241779497</v>
+        <v>0.379110251450677</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -88421,7 +88467,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>logit_binned_ohe_balanced_calibrated</t>
+          <t>random_forest_classifier_balanced</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -88431,47 +88477,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Best logistic model by CV ROC AUC</t>
+          <t>Selected classification model with threshold optimized on train OOF F1</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.881130493247186</v>
+        <v>0.9140224688816492</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6980576057044253</v>
+        <v>0.7727977418390275</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8403330948442059</v>
+        <v>0.8472481097273652</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5876274656093299</v>
+        <v>0.7068293562382115</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8771122911143998</v>
+        <v>0.9116048160891104</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6933517849967762</v>
+        <v>0.7693212731610033</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8415105952694979</v>
+        <v>0.8614261848237053</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5938943336712853</v>
+        <v>0.7076066790352504</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3140000487021511</v>
+        <v>0.5806481666978933</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8249769185838374</v>
+        <v>0.8643189569084092</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5933962264150944</v>
+        <v>0.6857798165137615</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7301218804410912</v>
+        <v>0.7437194262498964</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6546968514181629</v>
+        <v>0.7135754345491429</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -88888,10 +88934,10 @@
         <v>0.00897639626375045</v>
       </c>
       <c r="D10" t="n">
-        <v>72671.38933096816</v>
+        <v>72671.38933096814</v>
       </c>
       <c r="E10" t="n">
-        <v>888.4029424859095</v>
+        <v>888.4029424859123</v>
       </c>
       <c r="F10" t="n">
         <v>15350853973.39503</v>
@@ -88909,7 +88955,7 @@
         <v>0.7550502953367539</v>
       </c>
       <c r="K10" t="n">
-        <v>0.007765429060309091</v>
+        <v>0.007765429060309195</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>

--- a/slidedeck/data/model_slide_data.xlsx
+++ b/slidedeck/data/model_slide_data.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Selected model: random_forest_classifier_balanced | Baseline: random_classifier</t>
+          <t>Selected model: random_forest_classifier_balanced_calibrated | Baseline: random_classifier</t>
         </is>
       </c>
     </row>
@@ -86537,7 +86537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86799,44 +86799,44 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>logit_elasticnet_binned_ohe_balanced</t>
+          <t>random_forest_classifier_balanced_calibrated</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8811585985239313</v>
+        <v>0.9119921166430066</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004389213114772924</v>
+        <v>0.00399088077855746</v>
       </c>
       <c r="D6" t="n">
-        <v>0.697863011313659</v>
+        <v>0.7668162634417706</v>
       </c>
       <c r="E6" t="n">
-        <v>0.005226812006440109</v>
+        <v>0.01115278984033312</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7936804073504355</v>
+        <v>0.868746815522225</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007895207356770791</v>
+        <v>0.003644794072609333</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5299742035267634</v>
+        <v>0.7324243310589672</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01168668866481574</v>
+        <v>0.01090800262412072</v>
       </c>
       <c r="J6" t="n">
-        <v>0.817759352154822</v>
+        <v>0.6657820855660914</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007653141302854197</v>
+        <v>0.008829824930161092</v>
       </c>
       <c r="L6" t="n">
-        <v>0.643112712468934</v>
+        <v>0.6974760717590649</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01065785074699211</v>
+        <v>0.007879200146788794</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -86845,44 +86845,44 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>logit_binned_ohe_balanced</t>
+          <t>logit_elasticnet_binned_ohe_balanced</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8811365072867504</v>
+        <v>0.8811585985239313</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004376531559578211</v>
+        <v>0.004389213114772924</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6979843583264473</v>
+        <v>0.697863011313659</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005228907087311024</v>
+        <v>0.005226812006440109</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7937369346877954</v>
+        <v>0.7936804073504355</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007635615319973337</v>
+        <v>0.007895207356770791</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5300480731232893</v>
+        <v>0.5299742035267634</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01132393851248348</v>
+        <v>0.01168668866481574</v>
       </c>
       <c r="J7" t="n">
         <v>0.817759352154822</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007869077870088134</v>
+        <v>0.007653141302854197</v>
       </c>
       <c r="L7" t="n">
-        <v>0.643169280418737</v>
+        <v>0.643112712468934</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01041661405314055</v>
+        <v>0.01065785074699211</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -86891,44 +86891,44 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>logit_binned_ohe_balanced_calibrated</t>
+          <t>logit_binned_ohe_balanced</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.881130493247186</v>
+        <v>0.8811365072867504</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004370391028659821</v>
+        <v>0.004376531559578211</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6980576057044253</v>
+        <v>0.6979843583264473</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005206617861945132</v>
+        <v>0.005228907087311024</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8403330948442059</v>
+        <v>0.7937369346877954</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002963045688369091</v>
+        <v>0.007635615319973337</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7111746540752869</v>
+        <v>0.5300480731232893</v>
       </c>
       <c r="I8" t="n">
-        <v>0.006902739266586057</v>
+        <v>0.01132393851248348</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5007047577418887</v>
+        <v>0.817759352154822</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01202107305064498</v>
+        <v>0.007869077870088134</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5876274656093299</v>
+        <v>0.643169280418737</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01020369228274071</v>
+        <v>0.01041661405314055</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -86937,44 +86937,44 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>logit_binned_ohe</t>
+          <t>logit_binned_ohe_balanced_calibrated</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8810525664936373</v>
+        <v>0.881130493247186</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004399871941074101</v>
+        <v>0.004370391028659821</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7000061433590246</v>
+        <v>0.6980576057044253</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005493287863198479</v>
+        <v>0.005206617861945132</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8419347122034452</v>
+        <v>0.8403330948442059</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003374486507193572</v>
+        <v>0.002963045688369091</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7108721305626722</v>
+        <v>0.7111746540752869</v>
       </c>
       <c r="I9" t="n">
-        <v>0.008712052271902962</v>
+        <v>0.006902739266586057</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5131418126936804</v>
+        <v>0.5007047577418887</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01331058829753436</v>
+        <v>0.01202107305064498</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5959828291514137</v>
+        <v>0.5876274656093299</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01093835291011654</v>
+        <v>0.01020369228274071</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -86983,44 +86983,44 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>logit_elasticnet_binned_ohe</t>
+          <t>logit_binned_ohe</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8810395947267043</v>
+        <v>0.8810525664936373</v>
       </c>
       <c r="C10" t="n">
-        <v>0.004397931763937513</v>
+        <v>0.004399871941074101</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7001044823040902</v>
+        <v>0.7000061433590246</v>
       </c>
       <c r="E10" t="n">
-        <v>0.005480282425292697</v>
+        <v>0.005493287863198479</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8418781848660852</v>
+        <v>0.8419347122034452</v>
       </c>
       <c r="G10" t="n">
-        <v>0.003073224702100414</v>
+        <v>0.003374486507193572</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7125897899704303</v>
+        <v>0.7108721305626722</v>
       </c>
       <c r="I10" t="n">
-        <v>0.00816064576127834</v>
+        <v>0.008712052271902962</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5098253380149947</v>
+        <v>0.5131418126936804</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01212448308129676</v>
+        <v>0.01331058829753436</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5943442370054564</v>
+        <v>0.5959828291514137</v>
       </c>
       <c r="M10" t="n">
-        <v>0.009979210756378148</v>
+        <v>0.01093835291011654</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -87029,44 +87029,44 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>logit_elastic_binned_woe_balanced</t>
+          <t>logit_elasticnet_binned_ohe</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8772949445020284</v>
+        <v>0.8810395947267043</v>
       </c>
       <c r="C11" t="n">
-        <v>0.003761449015753651</v>
+        <v>0.004397931763937513</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6915303944720554</v>
+        <v>0.7001044823040902</v>
       </c>
       <c r="E11" t="n">
-        <v>0.003401032940688927</v>
+        <v>0.005480282425292697</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7897235878172972</v>
+        <v>0.8418781848660852</v>
       </c>
       <c r="G11" t="n">
-        <v>0.005722608230804933</v>
+        <v>0.003073224702100414</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5243023863756335</v>
+        <v>0.7125897899704303</v>
       </c>
       <c r="I11" t="n">
-        <v>0.008539626904805182</v>
+        <v>0.00816064576127834</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8085565404088826</v>
+        <v>0.5098253380149947</v>
       </c>
       <c r="K11" t="n">
-        <v>0.006059201965162753</v>
+        <v>0.01212448308129676</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6360934863488088</v>
+        <v>0.5943442370054564</v>
       </c>
       <c r="M11" t="n">
-        <v>0.007341581998092306</v>
+        <v>0.009979210756378148</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -87075,44 +87075,44 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>logit_elastic_binned_woe</t>
+          <t>logit_elastic_binned_woe_balanced</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8771585297862465</v>
+        <v>0.8772949445020284</v>
       </c>
       <c r="C12" t="n">
-        <v>0.003848776251252489</v>
+        <v>0.003761449015753651</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6930046960949421</v>
+        <v>0.6915303944720554</v>
       </c>
       <c r="E12" t="n">
-        <v>0.003656414022245295</v>
+        <v>0.003401032940688927</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8377705642287078</v>
+        <v>0.7897235878172972</v>
       </c>
       <c r="G12" t="n">
-        <v>0.002414774515868585</v>
+        <v>0.005722608230804933</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7167030676574802</v>
+        <v>0.5243023863756335</v>
       </c>
       <c r="I12" t="n">
-        <v>0.008626451904090178</v>
+        <v>0.008539626904805182</v>
       </c>
       <c r="J12" t="n">
-        <v>0.473261507079879</v>
+        <v>0.8085565404088826</v>
       </c>
       <c r="K12" t="n">
-        <v>0.01102548890008316</v>
+        <v>0.006059201965162753</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5700107706623559</v>
+        <v>0.6360934863488088</v>
       </c>
       <c r="M12" t="n">
-        <v>0.008637340913124606</v>
+        <v>0.007341581998092306</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -87121,44 +87121,44 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>logit_binned_woe</t>
+          <t>logit_elastic_binned_woe</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8771509619122287</v>
+        <v>0.8771585297862465</v>
       </c>
       <c r="C13" t="n">
-        <v>0.003836771048671129</v>
+        <v>0.003848776251252489</v>
       </c>
       <c r="D13" t="n">
-        <v>0.69300001724452</v>
+        <v>0.6930046960949421</v>
       </c>
       <c r="E13" t="n">
-        <v>0.003681078766040902</v>
+        <v>0.003656414022245295</v>
       </c>
       <c r="F13" t="n">
-        <v>0.837619832354658</v>
+        <v>0.8377705642287078</v>
       </c>
       <c r="G13" t="n">
-        <v>0.002470388242247739</v>
+        <v>0.002414774515868585</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7162381448730094</v>
+        <v>0.7167030676574802</v>
       </c>
       <c r="I13" t="n">
-        <v>0.009761304644855832</v>
+        <v>0.008626451904090178</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4729297633946581</v>
+        <v>0.473261507079879</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0107632093123463</v>
+        <v>0.01102548890008316</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5696159324654674</v>
+        <v>0.5700107706623559</v>
       </c>
       <c r="M13" t="n">
-        <v>0.008343765434171466</v>
+        <v>0.008637340913124606</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -87167,44 +87167,44 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>logit_elasticnet_robust_scaler_balanced</t>
+          <t>logit_binned_woe</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.867810003520171</v>
+        <v>0.8771509619122287</v>
       </c>
       <c r="C14" t="n">
-        <v>0.005528704925116762</v>
+        <v>0.003836771048671129</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6694910817508173</v>
+        <v>0.69300001724452</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01112195718805921</v>
+        <v>0.003681078766040902</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7869163213810961</v>
+        <v>0.837619832354658</v>
       </c>
       <c r="G14" t="n">
-        <v>0.007059674046021744</v>
+        <v>0.002470388242247739</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5204537102469808</v>
+        <v>0.7162381448730094</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01025794161469152</v>
+        <v>0.009761304644855832</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7957050635756155</v>
+        <v>0.4729297633946581</v>
       </c>
       <c r="K14" t="n">
-        <v>0.01105879664650136</v>
+        <v>0.0107632093123463</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6292835523135512</v>
+        <v>0.5696159324654674</v>
       </c>
       <c r="M14" t="n">
-        <v>0.01061365046270664</v>
+        <v>0.008343765434171466</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -87213,44 +87213,44 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>logit_elasticnet_robust_scaler</t>
+          <t>logit_elasticnet_robust_scaler_balanced</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.867526389543505</v>
+        <v>0.867810003520171</v>
       </c>
       <c r="C15" t="n">
-        <v>0.005529273069482899</v>
+        <v>0.005528704925116762</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6745461453118697</v>
+        <v>0.6694910817508173</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01096817627836946</v>
+        <v>0.01112195718805921</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8284249714713926</v>
+        <v>0.7869163213810961</v>
       </c>
       <c r="G15" t="n">
-        <v>0.002082293169188209</v>
+        <v>0.007059674046021744</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6843062922460865</v>
+        <v>0.5204537102469808</v>
       </c>
       <c r="I15" t="n">
-        <v>0.006041007482650775</v>
+        <v>0.01025794161469152</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4548537530609146</v>
+        <v>0.7957050635756155</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01057163743379905</v>
+        <v>0.01105879664650136</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5464187873581289</v>
+        <v>0.6292835523135512</v>
       </c>
       <c r="M15" t="n">
-        <v>0.008389729914154242</v>
+        <v>0.01061365046270664</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -87259,44 +87259,44 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>classic_logit_robust_scaler</t>
+          <t>logit_elasticnet_robust_scaler</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8675160644922242</v>
+        <v>0.867526389543505</v>
       </c>
       <c r="C16" t="n">
-        <v>0.005518549551175742</v>
+        <v>0.005529273069482899</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6745771081576786</v>
+        <v>0.6745461453118697</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01097031333685288</v>
+        <v>0.01096817627836946</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8284814970336194</v>
+        <v>0.8284249714713926</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001986574841447083</v>
+        <v>0.002082293169188209</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6842941667433381</v>
+        <v>0.6843062922460865</v>
       </c>
       <c r="I16" t="n">
-        <v>0.005884323395802298</v>
+        <v>0.006041007482650775</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4553512654987255</v>
+        <v>0.4548537530609146</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01054622802916655</v>
+        <v>0.01057163743379905</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5467708451685505</v>
+        <v>0.5464187873581289</v>
       </c>
       <c r="M16" t="n">
-        <v>0.008200986880072232</v>
+        <v>0.008389729914154242</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -87305,44 +87305,44 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>random_classifier</t>
+          <t>classic_logit_robust_scaler</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5018559714056471</v>
+        <v>0.8675160644922242</v>
       </c>
       <c r="C17" t="n">
-        <v>0.001720555585391747</v>
+        <v>0.005518549551175742</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2279191500425641</v>
+        <v>0.6745771081576786</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0006133047160225449</v>
+        <v>0.01097031333685288</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6535903477494552</v>
+        <v>0.8284814970336194</v>
       </c>
       <c r="G17" t="n">
-        <v>0.00121384248121297</v>
+        <v>0.001986574841447083</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2302047781569966</v>
+        <v>0.6842941667433381</v>
       </c>
       <c r="I17" t="n">
-        <v>0.002725037444141857</v>
+        <v>0.005884323395802298</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2236963407853673</v>
+        <v>0.4553512654987255</v>
       </c>
       <c r="K17" t="n">
-        <v>0.002661475279300156</v>
+        <v>0.01054622802916655</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2269038960423601</v>
+        <v>0.5467708451685505</v>
       </c>
       <c r="M17" t="n">
-        <v>0.002692826940019715</v>
+        <v>0.008200986880072232</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -87351,46 +87351,92 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>random_classifier</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.5018559714056471</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.001720555585391747</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.2279191500425641</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.0006133047160225449</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.6535903477494552</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.00121384248121297</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2302047781569966</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.002725037444141857</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.2236963407853673</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.002661475279300156</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.2269038960423601</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.002692826940019715</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>always_true_classifier</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B19" t="n">
         <v>0.5</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C19" t="n">
         <v>0</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D19" t="n">
         <v>0.2272530286210917</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E19" t="n">
         <v>3.884716467977554e-05</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F19" t="n">
         <v>0.2272530286210917</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G19" t="n">
         <v>3.884716467977554e-05</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H19" t="n">
         <v>0.2272530286210917</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I19" t="n">
         <v>3.884716467977554e-05</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L19" t="n">
         <v>0.3703442118613253</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M19" t="n">
         <v>5.158293634861289e-05</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -87483,44 +87529,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>random_forest_classifier_balanced</t>
+          <t>random_forest_classifier_balanced_calibrated</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9140224688816492</v>
+        <v>0.9119921166430066</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004096515051063659</v>
+        <v>0.00399088077855746</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7727977418390275</v>
+        <v>0.7668162634417706</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01129734405204536</v>
+        <v>0.01115278984033312</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8472481097273652</v>
+        <v>0.868746815522225</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005891976215397637</v>
+        <v>0.003644794072609333</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6269140050499862</v>
+        <v>0.7324243310589672</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01131547974546328</v>
+        <v>0.01090800262412072</v>
       </c>
       <c r="J2" t="n">
-        <v>0.810131034288428</v>
+        <v>0.6657820855660914</v>
       </c>
       <c r="K2" t="n">
-        <v>0.006975526899547858</v>
+        <v>0.008829824930161092</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7068293562382115</v>
+        <v>0.6974760717590649</v>
       </c>
       <c r="M2" t="n">
-        <v>0.009790777061447854</v>
+        <v>0.007879200146788794</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -87727,7 +87773,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>random_forest_classifier_balanced</t>
+          <t>random_forest_classifier_balanced_calibrated</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -87736,25 +87782,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9116048160891104</v>
+        <v>0.9093468740123026</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7693212731610033</v>
+        <v>0.7624737774930801</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8614261848237053</v>
+        <v>0.8600193440604942</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7076066790352504</v>
+        <v>0.7053488802517121</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6798573975044563</v>
+        <v>0.6761887863733144</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7377176015473887</v>
+        <v>0.7371373307543521</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5806481666978933</v>
+        <v>0.3937199960935918</v>
       </c>
       <c r="J2" t="n">
         <v>22746</v>
@@ -87839,10 +87885,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1741358393978058</v>
+        <v>0.1747790284180038</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -87855,10 +87901,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1461279336467704</v>
+        <v>0.1494341604954746</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -87871,10 +87917,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09811580318990407</v>
+        <v>0.1005686191795417</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -87887,10 +87933,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09531998536472823</v>
+        <v>0.09475866535750732</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -87899,14 +87945,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Revenue From Client Past Two Years (USD)</t>
+          <t>Ratio Days Identified To Total Days</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.09313218691299484</v>
+        <v>0.08103663900141232</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -87915,14 +87961,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ratio Days Identified To Total Days</t>
+          <t>Elapsed Days In Sales Stage</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08197809041557944</v>
+        <v>0.07867670116505286</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -87931,14 +87977,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Elapsed Days In Sales Stage</t>
+          <t>Ratio Days Validated To Total Days</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0800428785162902</v>
+        <v>0.07294844217115008</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -87947,14 +87993,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ratio Days Validated To Total Days</t>
+          <t>Revenue From Client Past Two Years (USD)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.073859846596819</v>
+        <v>0.02238493633746643</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -87967,10 +88013,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.04568964660543632</v>
+        <v>0.01151176103131319</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -87979,11 +88025,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Region</t>
+          <t>Competitor Type</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03468392733196007</v>
+        <v>0.009252843757919399</v>
       </c>
       <c r="C11" t="n">
         <v>6</v>
@@ -87995,14 +88041,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Supplies Subgroup</t>
+          <t>Region</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03153107686010778</v>
+        <v>0.00581547670593983</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -88011,14 +88057,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Competitor Type</t>
+          <t>Supplies Subgroup</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0189935185618011</v>
+        <v>0.003213789773600941</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -88031,10 +88077,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01235550098241272</v>
+        <v>0.003115114909689344</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -88043,14 +88089,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Client Size By Revenue (USD)</t>
+          <t>Supplies Group</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.007604936826221313</v>
+        <v>0.002216532922617283</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -88059,14 +88105,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Supplies Group</t>
+          <t>Client Size By Revenue (USD)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.00642882879116884</v>
+        <v>0.001891112710660577</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -88131,19 +88177,19 @@
         <v>2275</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01414954902385034</v>
+        <v>0.01451852289738244</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002637362637362637</v>
+        <v>0.002197802197802198</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001160541586073501</v>
+        <v>0.0009671179883945841</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001160541586073501</v>
+        <v>0.0009671179883945841</v>
       </c>
     </row>
     <row r="3">
@@ -88154,19 +88200,19 @@
         <v>2275</v>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03513692952501519</v>
+        <v>0.01686480555915209</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007912087912087912</v>
+        <v>0.01054945054945055</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003481624758220503</v>
+        <v>0.004642166344294004</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004642166344294004</v>
+        <v>0.005609284332688588</v>
       </c>
     </row>
     <row r="4">
@@ -88177,16 +88223,16 @@
         <v>2274</v>
       </c>
       <c r="C4" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>0.06563938808025802</v>
+        <v>0.02090919177209684</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01715039577836412</v>
+        <v>0.01495162708883025</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007543520309477757</v>
+        <v>0.006576402321083172</v>
       </c>
       <c r="G4" t="n">
         <v>0.01218568665377176</v>
@@ -88200,19 +88246,19 @@
         <v>2275</v>
       </c>
       <c r="C5" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D5" t="n">
-        <v>0.112815668938653</v>
+        <v>0.02911679204916495</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02857142857142857</v>
+        <v>0.03252747252747253</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01257253384912959</v>
+        <v>0.01431334622823984</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02475822050290135</v>
+        <v>0.0264990328820116</v>
       </c>
     </row>
     <row r="6">
@@ -88223,19 +88269,19 @@
         <v>2274</v>
       </c>
       <c r="C6" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1834857245203665</v>
+        <v>0.04669792737753347</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07167985927880387</v>
+        <v>0.07255936675461741</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03152804642166344</v>
+        <v>0.03191489361702127</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0562862669245648</v>
+        <v>0.05841392649903288</v>
       </c>
     </row>
     <row r="7">
@@ -88246,19 +88292,19 @@
         <v>2275</v>
       </c>
       <c r="C7" t="n">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2787608390295248</v>
+        <v>0.08636258261597439</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09802197802197803</v>
+        <v>0.09582417582417582</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04313346228239845</v>
+        <v>0.04216634429400387</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09941972920696325</v>
+        <v>0.1005802707930367</v>
       </c>
     </row>
     <row r="8">
@@ -88269,19 +88315,19 @@
         <v>2274</v>
       </c>
       <c r="C8" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4110668124390828</v>
+        <v>0.1851374530616332</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2005277044854881</v>
+        <v>0.202726473175022</v>
       </c>
       <c r="F8" t="n">
-        <v>0.08820116054158607</v>
+        <v>0.08916827852998066</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1876208897485493</v>
+        <v>0.1897485493230174</v>
       </c>
     </row>
     <row r="9">
@@ -88292,19 +88338,19 @@
         <v>2275</v>
       </c>
       <c r="C9" t="n">
-        <v>820</v>
+        <v>832</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5738417493690567</v>
+        <v>0.3920592110480624</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3604395604395604</v>
+        <v>0.3657142857142857</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1586073500967118</v>
+        <v>0.1609284332688588</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3462282398452611</v>
+        <v>0.3506769825918762</v>
       </c>
     </row>
     <row r="10">
@@ -88315,19 +88361,19 @@
         <v>2274</v>
       </c>
       <c r="C10" t="n">
-        <v>1420</v>
+        <v>1415</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7392865038088421</v>
+        <v>0.6448956538300292</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6244503078276166</v>
+        <v>0.6222515391380826</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2746615087040619</v>
+        <v>0.2736943907156673</v>
       </c>
       <c r="G10" t="n">
-        <v>0.620889748549323</v>
+        <v>0.6243713733075436</v>
       </c>
     </row>
     <row r="11">
@@ -88338,16 +88384,16 @@
         <v>2275</v>
       </c>
       <c r="C11" t="n">
-        <v>1960</v>
+        <v>1942</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8871508979032245</v>
+        <v>0.830884702471582</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8615384615384616</v>
+        <v>0.8536263736263736</v>
       </c>
       <c r="F11" t="n">
-        <v>0.379110251450677</v>
+        <v>0.3756286266924565</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -88467,7 +88513,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>random_forest_classifier_balanced</t>
+          <t>random_forest_classifier_balanced_calibrated</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -88481,43 +88527,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9140224688816492</v>
+        <v>0.9119921166430066</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7727977418390275</v>
+        <v>0.7668162634417706</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8472481097273652</v>
+        <v>0.868746815522225</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7068293562382115</v>
+        <v>0.6974760717590649</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9116048160891104</v>
+        <v>0.9093468740123026</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7693212731610033</v>
+        <v>0.7624737774930801</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8614261848237053</v>
+        <v>0.8600193440604942</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7076066790352504</v>
+        <v>0.7053488802517121</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5806481666978933</v>
+        <v>0.3937199960935918</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8643189569084092</v>
+        <v>0.8617941326098016</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6857798165137615</v>
+        <v>0.6783934772761588</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7437194262498964</v>
+        <v>0.7450460160849017</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7135754345491429</v>
+        <v>0.7101592444778124</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -88934,10 +88980,10 @@
         <v>0.00897639626375045</v>
       </c>
       <c r="D10" t="n">
-        <v>72671.38933096814</v>
+        <v>72671.38933096816</v>
       </c>
       <c r="E10" t="n">
-        <v>888.4029424859123</v>
+        <v>888.4029424859095</v>
       </c>
       <c r="F10" t="n">
         <v>15350853973.39503</v>
@@ -88949,13 +88995,13 @@
         <v>292.2436425303598</v>
       </c>
       <c r="I10" t="n">
-        <v>65.3964681733629</v>
+        <v>65.39646817336293</v>
       </c>
       <c r="J10" t="n">
         <v>0.7550502953367539</v>
       </c>
       <c r="K10" t="n">
-        <v>0.007765429060309195</v>
+        <v>0.007765429060309135</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>

--- a/slidedeck/data/model_slide_data.xlsx
+++ b/slidedeck/data/model_slide_data.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,20 +439,25 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>variant</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>target</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>business_use</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>data_used</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -466,20 +471,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>Opportunity Result</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Prioritization and pipeline ranking</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>All available snapshot variables, including process timing fields</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Selected model: random_forest_classifier_balanced_calibrated | Baseline: random_classifier</t>
         </is>
@@ -493,20 +503,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>Opportunity Amount USD</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Sizing and aggregate forecasting</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>All available snapshot variables, including process timing fields</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Selected model: xgboost_boxcox | Baseline: random_regressor</t>
         </is>
@@ -86411,7 +86426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86422,55 +86437,75 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>variant</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>feature_set_label</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>n_features</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>features</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>selected_experiment</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>baseline_experiment</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>baseline_experiments</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>selection_rule</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>cv_r2_mean</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>cv_mae_mean</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>cv_mape_mean</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>test_r2</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>test_mae</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>test_mape</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -86484,43 +86519,61 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>dynamic snapshot features including process variables</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Supplies Group, Supplies Subgroup, Region, Route To Market, Elapsed Days In Sales Stage, Sales Stage Change Count, Total Days Identified Through Closing, Total Days Identified Through Qualified, Client Size By Revenue (USD), Client Size By Employee Count, Revenue From Client Past Two Years (USD), Competitor Type, Ratio Days Identified To Total Days, Ratio Days Validated To Total Days, Ratio Days Qualified To Total Days</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>xgboost_boxcox</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>random_regressor</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>random_regressor, mean_regressor, median_regressor</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Best regression model by CV Median APE, tie-broken by MAE</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="J2" t="n">
         <v>0.0623203668740866</v>
       </c>
-      <c r="G2" t="n">
+      <c r="K2" t="n">
         <v>65098.04976889039</v>
       </c>
-      <c r="H2" t="n">
+      <c r="L2" t="n">
         <v>164.1180190717068</v>
       </c>
-      <c r="I2" t="n">
+      <c r="M2" t="n">
         <v>0.06744429869476365</v>
       </c>
-      <c r="J2" t="n">
+      <c r="N2" t="n">
         <v>64992.90788129644</v>
       </c>
-      <c r="K2" t="n">
+      <c r="O2" t="n">
         <v>172.8593948797542</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Final model trained on full train split and scored on held-out test split.</t>
         </is>
@@ -86615,44 +86668,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>random_forest_classifier</t>
+          <t>xgboost</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9166263168114168</v>
+        <v>0.9289335942110577</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003872988600675628</v>
+        <v>0.003527407871848218</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7839932418273847</v>
+        <v>0.8220510203677585</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008734272456820515</v>
+        <v>0.004825880640177495</v>
       </c>
       <c r="F2" t="n">
-        <v>0.872025280380049</v>
+        <v>0.8830290054080316</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002396041169168135</v>
+        <v>0.003532180189114433</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7780935086023624</v>
+        <v>0.7850605314286611</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006833173590338825</v>
+        <v>0.008685026635091317</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6112255753969482</v>
+        <v>0.6682683763115628</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01110534936184623</v>
+        <v>0.01228800637509388</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6845835769255423</v>
+        <v>0.721930760279903</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007557192019724195</v>
+        <v>0.009391286879144227</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -86661,44 +86714,44 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>random_forest_classifier_balanced</t>
+          <t>xgboost_balanced</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9140224688816492</v>
+        <v>0.9278888031098301</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004096515051063659</v>
+        <v>0.003865538362931818</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7727977418390275</v>
+        <v>0.8201732397660738</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01129734405204536</v>
+        <v>0.005786951837644623</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8472481097273652</v>
+        <v>0.8617187370886805</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005891976215397637</v>
+        <v>0.005828457809596978</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6269140050499862</v>
+        <v>0.6569548149418704</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01131547974546328</v>
+        <v>0.0128465214422707</v>
       </c>
       <c r="J3" t="n">
-        <v>0.810131034288428</v>
+        <v>0.8199980206716109</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006975526899547858</v>
+        <v>0.005203380487629867</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7068293562382115</v>
+        <v>0.7294366189090045</v>
       </c>
       <c r="M3" t="n">
-        <v>0.009790777061447854</v>
+        <v>0.00921847219633906</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -86707,44 +86760,44 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>xgboost_balanced</t>
+          <t>random_forest_classifier</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9123912353315229</v>
+        <v>0.9166515478801441</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003497478880795551</v>
+        <v>0.003821374484398381</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7834938339761315</v>
+        <v>0.784059874637531</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006874214727794301</v>
+        <v>0.008533016088452618</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8296308779426493</v>
+        <v>0.8722513613273593</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005416385756810691</v>
+        <v>0.003087237794554009</v>
       </c>
       <c r="H4" t="n">
-        <v>0.58782909096241</v>
+        <v>0.7788362426685129</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009567443909138844</v>
+        <v>0.008550182771624214</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8385701345462218</v>
+        <v>0.6115572503554887</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004374874500207381</v>
+        <v>0.01197051352572175</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6911286780642751</v>
+        <v>0.6850810704050938</v>
       </c>
       <c r="M4" t="n">
-        <v>0.007225987703506406</v>
+        <v>0.009046236906951603</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -86753,44 +86806,44 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>xgboost</t>
+          <t>random_forest_classifier_balanced</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9123864805636017</v>
+        <v>0.9139847821357575</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003481238918302272</v>
+        <v>0.003913500729752192</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7863944206132294</v>
+        <v>0.7730135272426459</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005723900679462718</v>
+        <v>0.01048178571325011</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8712150847967752</v>
+        <v>0.8468712898054729</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002882573554126725</v>
+        <v>0.005882680545058485</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7763101530423991</v>
+        <v>0.6262976414573421</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008081353391280693</v>
+        <v>0.01139080764969362</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6087382193879339</v>
+        <v>0.8092190312424614</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01125925573472648</v>
+        <v>0.006228867449051375</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6823398309631026</v>
+        <v>0.7060883599461392</v>
       </c>
       <c r="M5" t="n">
-        <v>0.008407140022573497</v>
+        <v>0.009597288044118277</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -86803,40 +86856,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9119921166430066</v>
+        <v>0.9119067937133698</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00399088077855746</v>
+        <v>0.004023626536093945</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7668162634417706</v>
+        <v>0.7665254818664221</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01115278984033312</v>
+        <v>0.01153895645575349</v>
       </c>
       <c r="F6" t="n">
-        <v>0.868746815522225</v>
+        <v>0.8687845051474865</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003644794072609333</v>
+        <v>0.003772569022227441</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7324243310589672</v>
+        <v>0.7323542393028306</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01090800262412072</v>
+        <v>0.01126666485400947</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6657820855660914</v>
+        <v>0.6661965074475666</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008829824930161092</v>
+        <v>0.009519772006363208</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6974760717590649</v>
+        <v>0.6976658253851086</v>
       </c>
       <c r="M6" t="n">
-        <v>0.007879200146788794</v>
+        <v>0.008233140636698871</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -87533,40 +87586,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9119921166430066</v>
+        <v>0.9119067937133698</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00399088077855746</v>
+        <v>0.004023626536093945</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7668162634417706</v>
+        <v>0.7665254818664221</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01115278984033312</v>
+        <v>0.01153895645575349</v>
       </c>
       <c r="F2" t="n">
-        <v>0.868746815522225</v>
+        <v>0.8687845051474865</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003644794072609333</v>
+        <v>0.003772569022227441</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7324243310589672</v>
+        <v>0.7323542393028306</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01090800262412072</v>
+        <v>0.01126666485400947</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6657820855660914</v>
+        <v>0.6661965074475666</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008829824930161092</v>
+        <v>0.009519772006363208</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6974760717590649</v>
+        <v>0.6976658253851086</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007879200146788794</v>
+        <v>0.008233140636698871</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -87782,25 +87835,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9093468740123026</v>
+        <v>0.9094663881378598</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7624737774930801</v>
+        <v>0.7632744530484556</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8600193440604942</v>
+        <v>0.8209355491075354</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7053488802517121</v>
+        <v>0.3853930888788291</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6761887863733144</v>
+        <v>0.876458476321208</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7371373307543521</v>
+        <v>0.2470019342359768</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3937199960935918</v>
+        <v>0.8157897839479512</v>
       </c>
       <c r="J2" t="n">
         <v>22746</v>
@@ -87885,7 +87938,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1747790284180038</v>
+        <v>0.1756475155478004</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
@@ -87901,7 +87954,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1494341604954746</v>
+        <v>0.1483384244203815</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
@@ -87917,7 +87970,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1005686191795417</v>
+        <v>0.1009702049216645</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
@@ -87933,7 +87986,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09475866535750732</v>
+        <v>0.0943525606323945</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
@@ -87949,7 +88002,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08103663900141232</v>
+        <v>0.08033291463487686</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
@@ -87965,7 +88018,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07867670116505286</v>
+        <v>0.07903757235953845</v>
       </c>
       <c r="C7" t="n">
         <v>3</v>
@@ -87981,7 +88034,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07294844217115008</v>
+        <v>0.07259293999335277</v>
       </c>
       <c r="C8" t="n">
         <v>3</v>
@@ -87997,7 +88050,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02238493633746643</v>
+        <v>0.02259978252242835</v>
       </c>
       <c r="C9" t="n">
         <v>12</v>
@@ -88013,7 +88066,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01151176103131319</v>
+        <v>0.01152854081372256</v>
       </c>
       <c r="C10" t="n">
         <v>12</v>
@@ -88029,7 +88082,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.009252843757919399</v>
+        <v>0.009424398241361494</v>
       </c>
       <c r="C11" t="n">
         <v>6</v>
@@ -88045,7 +88098,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.00581547670593983</v>
+        <v>0.00576922804587656</v>
       </c>
       <c r="C12" t="n">
         <v>18</v>
@@ -88061,7 +88114,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.003213789773600941</v>
+        <v>0.003212923607260055</v>
       </c>
       <c r="C13" t="n">
         <v>30</v>
@@ -88077,7 +88130,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.003115114909689344</v>
+        <v>0.003105791212273941</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
@@ -88093,7 +88146,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.002216532922617283</v>
+        <v>0.002218923441886486</v>
       </c>
       <c r="C15" t="n">
         <v>9</v>
@@ -88109,7 +88162,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.001891112710660577</v>
+        <v>0.001885309535012338</v>
       </c>
       <c r="C16" t="n">
         <v>12</v>
@@ -88177,19 +88230,19 @@
         <v>2275</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01451852289738244</v>
+        <v>0.01449828235584853</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002197802197802198</v>
+        <v>0.002637362637362637</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0009671179883945841</v>
+        <v>0.001160541586073501</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0009671179883945841</v>
+        <v>0.001160541586073501</v>
       </c>
     </row>
     <row r="3">
@@ -88200,16 +88253,16 @@
         <v>2275</v>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01686480555915209</v>
+        <v>0.01683626805935121</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01054945054945055</v>
+        <v>0.01010989010989011</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004642166344294004</v>
+        <v>0.004448742746615087</v>
       </c>
       <c r="G3" t="n">
         <v>0.005609284332688588</v>
@@ -88223,19 +88276,19 @@
         <v>2274</v>
       </c>
       <c r="C4" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02090919177209684</v>
+        <v>0.02082096500885975</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01495162708883025</v>
+        <v>0.01627088830255057</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006576402321083172</v>
+        <v>0.007156673114119922</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01218568665377176</v>
+        <v>0.01276595744680851</v>
       </c>
     </row>
     <row r="5">
@@ -88246,19 +88299,19 @@
         <v>2275</v>
       </c>
       <c r="C5" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02911679204916495</v>
+        <v>0.0289433117310839</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03252747252747253</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01431334622823984</v>
+        <v>0.01257253384912959</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0264990328820116</v>
+        <v>0.02533849129593811</v>
       </c>
     </row>
     <row r="6">
@@ -88269,19 +88322,19 @@
         <v>2274</v>
       </c>
       <c r="C6" t="n">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04669792737753347</v>
+        <v>0.04643635247062008</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07255936675461741</v>
+        <v>0.07563764291996482</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03191489361702127</v>
+        <v>0.0332688588007737</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05841392649903288</v>
+        <v>0.0586073500967118</v>
       </c>
     </row>
     <row r="7">
@@ -88292,19 +88345,19 @@
         <v>2275</v>
       </c>
       <c r="C7" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08636258261597439</v>
+        <v>0.08622368192399069</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09582417582417582</v>
+        <v>0.09626373626373626</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04216634429400387</v>
+        <v>0.04235976789168278</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1005802707930367</v>
+        <v>0.1009671179883946</v>
       </c>
     </row>
     <row r="8">
@@ -88315,19 +88368,19 @@
         <v>2274</v>
       </c>
       <c r="C8" t="n">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1851374530616332</v>
+        <v>0.1853982213204713</v>
       </c>
       <c r="E8" t="n">
-        <v>0.202726473175022</v>
+        <v>0.2005277044854881</v>
       </c>
       <c r="F8" t="n">
-        <v>0.08916827852998066</v>
+        <v>0.08820116054158607</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1897485493230174</v>
+        <v>0.1891682785299806</v>
       </c>
     </row>
     <row r="9">
@@ -88338,19 +88391,19 @@
         <v>2275</v>
       </c>
       <c r="C9" t="n">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3920592110480624</v>
+        <v>0.392163707147907</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3657142857142857</v>
+        <v>0.3630769230769231</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1609284332688588</v>
+        <v>0.1597678916827853</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3506769825918762</v>
+        <v>0.3489361702127659</v>
       </c>
     </row>
     <row r="10">
@@ -88361,19 +88414,19 @@
         <v>2274</v>
       </c>
       <c r="C10" t="n">
-        <v>1415</v>
+        <v>1424</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6448956538300292</v>
+        <v>0.6454670500870625</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6222515391380826</v>
+        <v>0.6262093227792436</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2736943907156673</v>
+        <v>0.2754352030947775</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6243713733075436</v>
+        <v>0.6243713733075434</v>
       </c>
     </row>
     <row r="11">
@@ -88387,7 +88440,7 @@
         <v>1942</v>
       </c>
       <c r="D11" t="n">
-        <v>0.830884702471582</v>
+        <v>0.8311574814079146</v>
       </c>
       <c r="E11" t="n">
         <v>0.8536263736263736</v>
@@ -88410,7 +88463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88421,85 +88474,105 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>variant</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>feature_set_label</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>n_features</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>features</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>selected_experiment</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>baseline_experiment</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>selection_rule</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>cv_roc_auc_mean</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>cv_pr_auc_mean</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>cv_accuracy_mean</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>cv_f1_mean</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>test_roc_auc</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>test_pr_auc</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>test_accuracy</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>test_f1</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>train_selected_threshold</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>train_selected_threshold_accuracy</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>train_selected_threshold_precision</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>train_selected_threshold_recall</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>train_selected_threshold_f1</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -88513,59 +88586,77 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>dynamic snapshot features including process variables</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Supplies Group, Supplies Subgroup, Region, Route To Market, Elapsed Days In Sales Stage, Sales Stage Change Count, Total Days Identified Through Closing, Total Days Identified Through Qualified, Client Size By Revenue (USD), Client Size By Employee Count, Revenue From Client Past Two Years (USD), Competitor Type, Ratio Days Identified To Total Days, Ratio Days Validated To Total Days, Ratio Days Qualified To Total Days</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>random_forest_classifier_balanced_calibrated</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>random_classifier</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
-          <t>Selected classification model with threshold optimized on train OOF F1</t>
+          <t>Selected classification model with threshold chosen on train OOF to maximize precision subject to recall &gt;= 25%</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>0.9119921166430066</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.7668162634417706</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.868746815522225</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.6974760717590649</v>
-      </c>
       <c r="I2" t="n">
-        <v>0.9093468740123026</v>
+        <v>0.9119067937133698</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7624737774930801</v>
+        <v>0.7665254818664221</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8600193440604942</v>
+        <v>0.8687845051474865</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7053488802517121</v>
+        <v>0.6976658253851086</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3937199960935918</v>
+        <v>0.9094663881378598</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8617941326098016</v>
+        <v>0.7632744530484556</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6783934772761588</v>
+        <v>0.8209355491075354</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7450460160849017</v>
+        <v>0.3853930888788291</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7101592444778124</v>
-      </c>
-      <c r="R2" t="inlineStr">
+        <v>0.8157897839479512</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.8224709362576075</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.8863836017569546</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.2509742144100821</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.3911863530628069</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>Final model trained on full train split and scored on held-out test split.</t>
         </is>
@@ -88995,13 +89086,13 @@
         <v>292.2436425303598</v>
       </c>
       <c r="I10" t="n">
-        <v>65.39646817336293</v>
+        <v>65.3964681733629</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7550502953367539</v>
+        <v>0.7550502953367538</v>
       </c>
       <c r="K10" t="n">
-        <v>0.007765429060309135</v>
+        <v>0.007765429060309128</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>

--- a/slidedeck/data/model_slide_data.xlsx
+++ b/slidedeck/data/model_slide_data.xlsx
@@ -87841,19 +87841,19 @@
         <v>0.7632744530484556</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8209355491075354</v>
+        <v>0.8582168293326299</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3853930888788291</v>
+        <v>0.7055063464523788</v>
       </c>
       <c r="G2" t="n">
-        <v>0.876458476321208</v>
+        <v>0.6682234907455458</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2470019342359768</v>
+        <v>0.7471953578336558</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8157897839479512</v>
+        <v>0.3783092077038575</v>
       </c>
       <c r="J2" t="n">
         <v>22746</v>
@@ -88233,7 +88233,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01449828235584853</v>
+        <v>0.01449828235584854</v>
       </c>
       <c r="E2" t="n">
         <v>0.002637362637362637</v>
@@ -88256,7 +88256,7 @@
         <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01683626805935121</v>
+        <v>0.01683626805935122</v>
       </c>
       <c r="E3" t="n">
         <v>0.01010989010989011</v>
@@ -88279,7 +88279,7 @@
         <v>37</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02082096500885975</v>
+        <v>0.02082096500885976</v>
       </c>
       <c r="E4" t="n">
         <v>0.01627088830255057</v>
@@ -88302,7 +88302,7 @@
         <v>65</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0289433117310839</v>
+        <v>0.02894331173108391</v>
       </c>
       <c r="E5" t="n">
         <v>0.02857142857142857</v>
@@ -88348,7 +88348,7 @@
         <v>219</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08622368192399069</v>
+        <v>0.08622368192399071</v>
       </c>
       <c r="E7" t="n">
         <v>0.09626373626373626</v>
@@ -88394,7 +88394,7 @@
         <v>826</v>
       </c>
       <c r="D9" t="n">
-        <v>0.392163707147907</v>
+        <v>0.3921637071479071</v>
       </c>
       <c r="E9" t="n">
         <v>0.3630769230769231</v>
@@ -88417,7 +88417,7 @@
         <v>1424</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6454670500870625</v>
+        <v>0.6454670500870626</v>
       </c>
       <c r="E10" t="n">
         <v>0.6262093227792436</v>
@@ -88614,7 +88614,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Selected classification model with threshold chosen on train OOF to maximize precision subject to recall &gt;= 25%</t>
+          <t>Selected classification model with threshold optimized on train OOF F1</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -88636,25 +88636,25 @@
         <v>0.7632744530484556</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8209355491075354</v>
+        <v>0.8582168293326299</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3853930888788291</v>
+        <v>0.7055063464523788</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.8157897839479512</v>
+        <v>0.3783092077038575</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8224709362576075</v>
+        <v>0.8599853032615454</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8863836017569546</v>
+        <v>0.6706723680330287</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2509742144100821</v>
+        <v>0.7542492330652516</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3911863530628069</v>
+        <v>0.710009756097561</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
